--- a/Audit_QMOD_Master_Templates.xlsx
+++ b/Audit_QMOD_Master_Templates.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf349213c04ea4156"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOP Audit" sheetId="2" r:id="R36d94fdf61e54da2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wireless BAS" sheetId="3" r:id="Rc36e61d69778449a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCS" sheetId="4" r:id="R29904d2d90c543c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wired BAS" sheetId="5" r:id="R857aa207c59c4f00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf9be9db2d0064528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOP Audit" sheetId="2" r:id="R26149e645f8d4123"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wireless BAS" sheetId="3" r:id="Rff6f5956eeea4d22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCS" sheetId="4" r:id="Ra2478189e1464e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wired BAS" sheetId="5" r:id="Rddf43723c6414bb5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,7 +77,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -85,16 +85,10 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -116,31 +110,25 @@
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -344,74 +332,82 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="88" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="92" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="4" t="str">
         <x:v>Audit QMOD – Master Audit Templates</x:v>
       </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
+      <x:c r="B1" s="4"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
+      <x:c r="F1" s="4"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="A3" s="12" t="str">
         <x:v>Purpose</x:v>
       </x:c>
-      <x:c r="B3" s="15" t="str">
-        <x:v>Edit this single workbook, then replace Audit_QMOD_Master_Templates.xlsx in the GitHub repository. Users who open Audit QMOD online will automatically receive the latest templates.</x:v>
+      <x:c r="B3" s="13" t="str">
+        <x:v>Edit this workbook and replace Audit_QMOD_Master_Templates.xlsx in the GitHub repository. New audits will use the latest template loaded from the repository.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="A4" s="12" t="str">
         <x:v>Core sheets</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
+      <x:c r="B4" s="13" t="str">
         <x:v>SOP Audit, Wireless BAS, PCS and Wired BAS are the four core audit templates.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="str">
+      <x:c r="A5" s="12" t="str">
+        <x:v>Response columns</x:v>
+      </x:c>
+      <x:c r="B5" s="13" t="str">
+        <x:v>Status, Evidence Link / Reference, Auditor Remark and Remark are intentionally blank here. They mirror the audit input/output fields; actual auditor responses are stored by Audit QMOD during an audit.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="12" t="str">
+        <x:v>Evidence Expected</x:v>
+      </x:c>
+      <x:c r="B6" s="13" t="str">
+        <x:v>Keep this populated. Audit QMOD shows it prominently under every audit check so the auditor knows what evidence to verify.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12" t="str">
         <x:v>Add another SOP</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="str">
-        <x:v>Duplicate the 'SOP Audit' sheet, rename the copied sheet to start with 'SOP - ' (for example 'SOP - Complaint'), then change Template Name / Template ID and checklist rows.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="14" t="str">
+      <x:c r="B7" s="13" t="str">
+        <x:v>Duplicate 'SOP Audit', rename the copy to start with 'SOP - ', then update Template Name / Template ID and checklist rows.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
         <x:v>Item ID</x:v>
       </x:c>
-      <x:c r="B6" s="15" t="str">
-        <x:v>Keep existing Item IDs stable when only changing wording. For a new checklist item, create a new unique Item ID. Do not reuse an ID for a different requirement.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="14" t="str">
+      <x:c r="B8" s="13" t="str">
+        <x:v>Keep an existing Item ID stable for wording changes. Use a new unique Item ID for a genuinely new requirement.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="str">
         <x:v>Active</x:v>
       </x:c>
-      <x:c r="B7" s="15" t="str">
-        <x:v>Set Active = No to temporarily hide a checklist row without deleting it.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="14" t="str">
+      <x:c r="B9" s="13" t="str">
+        <x:v>Set Active = No to hide a checklist row from new audits without deleting it.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="str">
         <x:v>Past audits</x:v>
       </x:c>
-      <x:c r="B8" s="15" t="str">
-        <x:v>Existing audit records keep a snapshot of the template used when that audit was created. Updating this workbook affects new audits only.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="14" t="str">
-        <x:v>Offline use</x:v>
-      </x:c>
-      <x:c r="B9" s="15" t="str">
-        <x:v>If the latest workbook cannot be reached, Audit QMOD uses the most recent successfully cached repository template.</x:v>
+      <x:c r="B10" s="13" t="str">
+        <x:v>Existing audits retain their checklist snapshot. Template changes affect new audits unless Update This Audit is explicitly used.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -428,88 +424,108 @@
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="7" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="50" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="20" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="17" t="str">
         <x:v>Audit QMOD – Repository Template</x:v>
       </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
+      <x:c r="B1" s="17"/>
+      <x:c r="C1" s="17"/>
+      <x:c r="D1" s="17"/>
+      <x:c r="E1" s="17"/>
+      <x:c r="F1" s="17"/>
+      <x:c r="G1" s="17"/>
+      <x:c r="H1" s="17"/>
+      <x:c r="I1" s="17"/>
+      <x:c r="J1" s="17"/>
+      <x:c r="K1" s="17"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="A3" s="9" t="str">
         <x:v>Template Type</x:v>
       </x:c>
-      <x:c r="B3" s="15" t="str">
+      <x:c r="B3" t="str">
         <x:v>SOP</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>Template ID</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
+      <x:c r="B4" t="str">
         <x:v>qos-network-audit</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>Template Name</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="str">
+      <x:c r="B5" t="str">
         <x:v>QUALITY OF SERVICE NETWORK AUDIT STANDARD OPERATING PROCEDURE</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="14" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>Template Version</x:v>
       </x:c>
-      <x:c r="B6" s="15" t="str">
+      <x:c r="B6" t="str">
         <x:v>1.0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="14" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>Effective Date</x:v>
       </x:c>
-      <x:c r="B7" s="15" t="str"/>
+      <x:c r="B7" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="14" t="str">
+      <x:c r="A8" s="9" t="str">
         <x:v>Source / Reference</x:v>
       </x:c>
-      <x:c r="B8" s="15" t="str"/>
+      <x:c r="B8" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="27" t="str">
+      <x:c r="A10" s="23" t="str">
         <x:v>Item ID</x:v>
       </x:c>
-      <x:c r="B10" s="27" t="str">
+      <x:c r="B10" s="23" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="str">
+      <x:c r="C10" s="23" t="str">
         <x:v>Section</x:v>
       </x:c>
-      <x:c r="D10" s="27" t="str">
+      <x:c r="D10" s="23" t="str">
         <x:v>Audit Check</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="str">
+      <x:c r="E10" s="23" t="str">
         <x:v>Evidence Expected</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="str">
+      <x:c r="F10" s="23" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G10" s="23" t="str">
+        <x:v>Evidence Link / Reference</x:v>
+      </x:c>
+      <x:c r="H10" s="23" t="str">
+        <x:v>Auditor Remark</x:v>
+      </x:c>
+      <x:c r="I10" s="23" t="str">
+        <x:v>Remark</x:v>
+      </x:c>
+      <x:c r="J10" s="23" t="str">
         <x:v>Guidance / Notes</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="str">
+      <x:c r="K10" s="23" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -520,17 +536,21 @@
       <x:c r="B11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="str">
+      <x:c r="C11" s="13" t="str">
         <x:v>Planning and Assignment</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="str">
+      <x:c r="D11" s="13" t="str">
         <x:v>State Office has identified target locations / sites / areas for assessment</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="str">
+      <x:c r="E11" s="13" t="str">
         <x:v>Target list / planning document</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="str"/>
-      <x:c r="G11" t="str">
+      <x:c r="F11" s="13" t="str"/>
+      <x:c r="G11" s="13" t="str"/>
+      <x:c r="H11" s="13" t="str"/>
+      <x:c r="I11" s="13" t="str"/>
+      <x:c r="J11" s="13" t="str"/>
+      <x:c r="K11" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -541,17 +561,21 @@
       <x:c r="B12" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="str">
+      <x:c r="C12" s="13" t="str">
         <x:v>Planning and Assignment</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="str">
+      <x:c r="D12" s="13" t="str">
         <x:v>Officer in charge is clearly assigned</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="str">
+      <x:c r="E12" s="13" t="str">
         <x:v>Email assignment / task list</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="str"/>
-      <x:c r="G12" t="str">
+      <x:c r="F12" s="13" t="str"/>
+      <x:c r="G12" s="13" t="str"/>
+      <x:c r="H12" s="13" t="str"/>
+      <x:c r="I12" s="13" t="str"/>
+      <x:c r="J12" s="13" t="str"/>
+      <x:c r="K12" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -562,17 +586,21 @@
       <x:c r="B13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="str">
+      <x:c r="C13" s="13" t="str">
         <x:v>Planning and Assignment</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="str">
+      <x:c r="D13" s="13" t="str">
         <x:v>Scope of work is clearly defined before field activity</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="str">
+      <x:c r="E13" s="13" t="str">
         <x:v>instruction email</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="str"/>
-      <x:c r="G13" t="str">
+      <x:c r="F13" s="13" t="str"/>
+      <x:c r="G13" s="13" t="str"/>
+      <x:c r="H13" s="13" t="str"/>
+      <x:c r="I13" s="13" t="str"/>
+      <x:c r="J13" s="13" t="str"/>
+      <x:c r="K13" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -583,17 +611,21 @@
       <x:c r="B14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="str">
+      <x:c r="C14" s="13" t="str">
         <x:v>Planning and Assignment</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="str">
+      <x:c r="D14" s="13" t="str">
         <x:v>Required tools, devices or access are prepared before activity</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="str">
+      <x:c r="E14" s="13" t="str">
         <x:v>Equipment checklist / system access record</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="str"/>
-      <x:c r="G14" t="str">
+      <x:c r="F14" s="13" t="str"/>
+      <x:c r="G14" s="13" t="str"/>
+      <x:c r="H14" s="13" t="str"/>
+      <x:c r="I14" s="13" t="str"/>
+      <x:c r="J14" s="13" t="str"/>
+      <x:c r="K14" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -604,17 +636,21 @@
       <x:c r="B15" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="str">
+      <x:c r="C15" s="13" t="str">
         <x:v>Execution and Fieldwork</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="str">
+      <x:c r="D15" s="13" t="str">
         <x:v>Activity is carried out according to approved plan or instruction</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="str">
+      <x:c r="E15" s="13" t="str">
         <x:v>Fieldwork record / log / photos</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="str"/>
-      <x:c r="G15" t="str">
+      <x:c r="F15" s="13" t="str"/>
+      <x:c r="G15" s="13" t="str"/>
+      <x:c r="H15" s="13" t="str"/>
+      <x:c r="I15" s="13" t="str"/>
+      <x:c r="J15" s="13" t="str"/>
+      <x:c r="K15" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -625,17 +661,21 @@
       <x:c r="B16" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="str">
+      <x:c r="C16" s="13" t="str">
         <x:v>Execution and Fieldwork</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="str">
+      <x:c r="D16" s="13" t="str">
         <x:v>Date, time, location and officer involved are recorded</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="str">
+      <x:c r="E16" s="13" t="str">
         <x:v>Attendance / site log / field form</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="str"/>
-      <x:c r="G16" t="str">
+      <x:c r="F16" s="13" t="str"/>
+      <x:c r="G16" s="13" t="str"/>
+      <x:c r="H16" s="13" t="str"/>
+      <x:c r="I16" s="13" t="str"/>
+      <x:c r="J16" s="13" t="str"/>
+      <x:c r="K16" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -646,17 +686,21 @@
       <x:c r="B17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="str">
+      <x:c r="C17" s="13" t="str">
         <x:v>Execution and Fieldwork</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="str">
+      <x:c r="D17" s="13" t="str">
         <x:v>Methodology used is consistent with SOP or technical requirement</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="str">
+      <x:c r="E17" s="13" t="str">
         <x:v>Test form / measurement setting / checklist</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="str"/>
-      <x:c r="G17" t="str">
+      <x:c r="F17" s="13" t="str"/>
+      <x:c r="G17" s="13" t="str"/>
+      <x:c r="H17" s="13" t="str"/>
+      <x:c r="I17" s="13" t="str"/>
+      <x:c r="J17" s="13" t="str"/>
+      <x:c r="K17" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -667,17 +711,21 @@
       <x:c r="B18" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="str">
+      <x:c r="C18" s="13" t="str">
         <x:v>Execution and Fieldwork</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="str">
+      <x:c r="D18" s="13" t="str">
         <x:v>Any issue during fieldwork is recorded</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="str">
+      <x:c r="E18" s="13" t="str">
         <x:v>Issue log / email / field remarks</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="str"/>
-      <x:c r="G18" t="str">
+      <x:c r="F18" s="13" t="str"/>
+      <x:c r="G18" s="13" t="str"/>
+      <x:c r="H18" s="13" t="str"/>
+      <x:c r="I18" s="13" t="str"/>
+      <x:c r="J18" s="13" t="str"/>
+      <x:c r="K18" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -688,17 +736,21 @@
       <x:c r="B19" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="str">
+      <x:c r="C19" s="13" t="str">
         <x:v>Execution and Fieldwork</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="str">
+      <x:c r="D19" s="13" t="str">
         <x:v>Any change from original plan is justified and approved</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="str">
+      <x:c r="E19" s="13" t="str">
         <x:v>Revised plan / approval email</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="str"/>
-      <x:c r="G19" t="str">
+      <x:c r="F19" s="13" t="str"/>
+      <x:c r="G19" s="13" t="str"/>
+      <x:c r="H19" s="13" t="str"/>
+      <x:c r="I19" s="13" t="str"/>
+      <x:c r="J19" s="13" t="str"/>
+      <x:c r="K19" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -709,17 +761,21 @@
       <x:c r="B20" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="str">
+      <x:c r="C20" s="13" t="str">
         <x:v>Data Collection and Data Integrity</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="str">
+      <x:c r="D20" s="13" t="str">
         <x:v>Required data fields are completely captured</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="str">
+      <x:c r="E20" s="13" t="str">
         <x:v>Completed data template / system record</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="str"/>
-      <x:c r="G20" t="str">
+      <x:c r="F20" s="13" t="str"/>
+      <x:c r="G20" s="13" t="str"/>
+      <x:c r="H20" s="13" t="str"/>
+      <x:c r="I20" s="13" t="str"/>
+      <x:c r="J20" s="13" t="str"/>
+      <x:c r="K20" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -730,17 +786,21 @@
       <x:c r="B21" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="str">
+      <x:c r="C21" s="13" t="str">
         <x:v>Data Collection and Data Integrity</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="str">
+      <x:c r="D21" s="13" t="str">
         <x:v>Data is checked for completeness before analysis</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="str">
+      <x:c r="E21" s="13" t="str">
         <x:v>QC checklist / review notes</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="str"/>
-      <x:c r="G21" t="str">
+      <x:c r="F21" s="13" t="str"/>
+      <x:c r="G21" s="13" t="str"/>
+      <x:c r="H21" s="13" t="str"/>
+      <x:c r="I21" s="13" t="str"/>
+      <x:c r="J21" s="13" t="str"/>
+      <x:c r="K21" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -751,17 +811,21 @@
       <x:c r="B22" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="str">
+      <x:c r="C22" s="13" t="str">
         <x:v>Data Collection and Data Integrity</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="str">
+      <x:c r="D22" s="13" t="str">
         <x:v>Abnormal, missing or inconsistent data is flagged</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="str">
+      <x:c r="E22" s="13" t="str">
         <x:v>Exception log / remarks</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="str"/>
-      <x:c r="G22" t="str">
+      <x:c r="F22" s="13" t="str"/>
+      <x:c r="G22" s="13" t="str"/>
+      <x:c r="H22" s="13" t="str"/>
+      <x:c r="I22" s="13" t="str"/>
+      <x:c r="J22" s="13" t="str"/>
+      <x:c r="K22" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -772,17 +836,21 @@
       <x:c r="B23" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="str">
+      <x:c r="C23" s="13" t="str">
         <x:v>Data Collection and Data Integrity</x:v>
       </x:c>
-      <x:c r="D23" s="15" t="str">
+      <x:c r="D23" s="13" t="str">
         <x:v>Data is stored in official location</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="str">
+      <x:c r="E23" s="13" t="str">
         <x:v>SharePoint / system / shared drive</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="str"/>
-      <x:c r="G23" t="str">
+      <x:c r="F23" s="13" t="str"/>
+      <x:c r="G23" s="13" t="str"/>
+      <x:c r="H23" s="13" t="str"/>
+      <x:c r="I23" s="13" t="str"/>
+      <x:c r="J23" s="13" t="str"/>
+      <x:c r="K23" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -793,17 +861,21 @@
       <x:c r="B24" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="str">
+      <x:c r="C24" s="13" t="str">
         <x:v>Analysis and Validation</x:v>
       </x:c>
-      <x:c r="D24" s="15" t="str">
+      <x:c r="D24" s="13" t="str">
         <x:v>Collected data is analysed according to required method</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="str">
+      <x:c r="E24" s="13" t="str">
         <x:v>Analysis file / calculation sheet / dashboard</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="str"/>
-      <x:c r="G24" t="str">
+      <x:c r="F24" s="13" t="str"/>
+      <x:c r="G24" s="13" t="str"/>
+      <x:c r="H24" s="13" t="str"/>
+      <x:c r="I24" s="13" t="str"/>
+      <x:c r="J24" s="13" t="str"/>
+      <x:c r="K24" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -814,17 +886,21 @@
       <x:c r="B25" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="str">
+      <x:c r="C25" s="13" t="str">
         <x:v>Analysis and Validation</x:v>
       </x:c>
-      <x:c r="D25" s="15" t="str">
+      <x:c r="D25" s="13" t="str">
         <x:v>Result is reviewed before reporting</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="str">
+      <x:c r="E25" s="13" t="str">
         <x:v>Review email / sign-off</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="str"/>
-      <x:c r="G25" t="str">
+      <x:c r="F25" s="13" t="str"/>
+      <x:c r="G25" s="13" t="str"/>
+      <x:c r="H25" s="13" t="str"/>
+      <x:c r="I25" s="13" t="str"/>
+      <x:c r="J25" s="13" t="str"/>
+      <x:c r="K25" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -835,17 +911,21 @@
       <x:c r="B26" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="str">
+      <x:c r="C26" s="13" t="str">
         <x:v>Analysis and Validation</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="str">
+      <x:c r="D26" s="13" t="str">
         <x:v>Failed / non-compliant result is properly identified</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="str">
+      <x:c r="E26" s="13" t="str">
         <x:v>Non-compliance list / finding summary (including FIR)</x:v>
       </x:c>
-      <x:c r="F26" s="15" t="str"/>
-      <x:c r="G26" t="str">
+      <x:c r="F26" s="13" t="str"/>
+      <x:c r="G26" s="13" t="str"/>
+      <x:c r="H26" s="13" t="str"/>
+      <x:c r="I26" s="13" t="str"/>
+      <x:c r="J26" s="13" t="str"/>
+      <x:c r="K26" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -856,17 +936,21 @@
       <x:c r="B27" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="str">
+      <x:c r="C27" s="13" t="str">
         <x:v>Analysis and Validation</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="str">
+      <x:c r="D27" s="13" t="str">
         <x:v>Supporting evidence matches the reported result</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="str">
+      <x:c r="E27" s="13" t="str">
         <x:v>Raw data vs report sample</x:v>
       </x:c>
-      <x:c r="F27" s="15" t="str"/>
-      <x:c r="G27" t="str">
+      <x:c r="F27" s="13" t="str"/>
+      <x:c r="G27" s="13" t="str"/>
+      <x:c r="H27" s="13" t="str"/>
+      <x:c r="I27" s="13" t="str"/>
+      <x:c r="J27" s="13" t="str"/>
+      <x:c r="K27" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -877,17 +961,21 @@
       <x:c r="B28" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="str">
+      <x:c r="C28" s="13" t="str">
         <x:v>Analysis and Validation</x:v>
       </x:c>
-      <x:c r="D28" s="15" t="str">
+      <x:c r="D28" s="13" t="str">
         <x:v>Any assumptions or exclusions are documented</x:v>
       </x:c>
-      <x:c r="E28" s="15" t="str">
+      <x:c r="E28" s="13" t="str">
         <x:v>Analysis note / justification</x:v>
       </x:c>
-      <x:c r="F28" s="15" t="str"/>
-      <x:c r="G28" t="str">
+      <x:c r="F28" s="13" t="str"/>
+      <x:c r="G28" s="13" t="str"/>
+      <x:c r="H28" s="13" t="str"/>
+      <x:c r="I28" s="13" t="str"/>
+      <x:c r="J28" s="13" t="str"/>
+      <x:c r="K28" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -898,17 +986,21 @@
       <x:c r="B29" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C29" s="15" t="str">
+      <x:c r="C29" s="13" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="D29" s="15" t="str">
+      <x:c r="D29" s="13" t="str">
         <x:v>Measurement results are entered into the Tracker</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="str">
+      <x:c r="E29" s="13" t="str">
         <x:v>Tracker</x:v>
       </x:c>
-      <x:c r="F29" s="15" t="str"/>
-      <x:c r="G29" t="str">
+      <x:c r="F29" s="13" t="str"/>
+      <x:c r="G29" s="13" t="str"/>
+      <x:c r="H29" s="13" t="str"/>
+      <x:c r="I29" s="13" t="str"/>
+      <x:c r="J29" s="13" t="str"/>
+      <x:c r="K29" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -919,17 +1011,21 @@
       <x:c r="B30" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C30" s="15" t="str">
+      <x:c r="C30" s="13" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="D30" s="15" t="str">
+      <x:c r="D30" s="13" t="str">
         <x:v>All mandatory fields in the tracker are completed</x:v>
       </x:c>
-      <x:c r="E30" s="15" t="str">
+      <x:c r="E30" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F30" s="15" t="str"/>
-      <x:c r="G30" t="str">
+      <x:c r="F30" s="13" t="str"/>
+      <x:c r="G30" s="13" t="str"/>
+      <x:c r="H30" s="13" t="str"/>
+      <x:c r="I30" s="13" t="str"/>
+      <x:c r="J30" s="13" t="str"/>
+      <x:c r="K30" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -940,17 +1036,21 @@
       <x:c r="B31" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C31" s="15" t="str">
+      <x:c r="C31" s="13" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="D31" s="15" t="str">
+      <x:c r="D31" s="13" t="str">
         <x:v>Operator / Service Provider information is correctly selected or entered</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="str">
+      <x:c r="E31" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F31" s="15" t="str"/>
-      <x:c r="G31" t="str">
+      <x:c r="F31" s="13" t="str"/>
+      <x:c r="G31" s="13" t="str"/>
+      <x:c r="H31" s="13" t="str"/>
+      <x:c r="I31" s="13" t="str"/>
+      <x:c r="J31" s="13" t="str"/>
+      <x:c r="K31" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -961,17 +1061,21 @@
       <x:c r="B32" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C32" s="15" t="str">
+      <x:c r="C32" s="13" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="D32" s="15" t="str">
+      <x:c r="D32" s="13" t="str">
         <x:v>Required measurement indicators are completely filled in</x:v>
       </x:c>
-      <x:c r="E32" s="15" t="str">
+      <x:c r="E32" s="13" t="str">
         <x:v>Tracker</x:v>
       </x:c>
-      <x:c r="F32" s="15" t="str"/>
-      <x:c r="G32" t="str">
+      <x:c r="F32" s="13" t="str"/>
+      <x:c r="G32" s="13" t="str"/>
+      <x:c r="H32" s="13" t="str"/>
+      <x:c r="I32" s="13" t="str"/>
+      <x:c r="J32" s="13" t="str"/>
+      <x:c r="K32" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -982,17 +1086,21 @@
       <x:c r="B33" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C33" s="15" t="str">
+      <x:c r="C33" s="13" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="D33" s="15" t="str">
+      <x:c r="D33" s="13" t="str">
         <x:v>Tracker format or template is not altered without approval</x:v>
       </x:c>
-      <x:c r="E33" s="15" t="str">
+      <x:c r="E33" s="13" t="str">
         <x:v>Tracker</x:v>
       </x:c>
-      <x:c r="F33" s="15" t="str"/>
-      <x:c r="G33" t="str">
+      <x:c r="F33" s="13" t="str"/>
+      <x:c r="G33" s="13" t="str"/>
+      <x:c r="H33" s="13" t="str"/>
+      <x:c r="I33" s="13" t="str"/>
+      <x:c r="J33" s="13" t="str"/>
+      <x:c r="K33" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1003,17 +1111,21 @@
       <x:c r="B34" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C34" s="15" t="str">
+      <x:c r="C34" s="13" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="D34" s="15" t="str">
+      <x:c r="D34" s="13" t="str">
         <x:v>Data entered in the tracker is consistent with source/raw measurement records</x:v>
       </x:c>
-      <x:c r="E34" s="15" t="str">
+      <x:c r="E34" s="13" t="str">
         <x:v>Raw data /measurement log</x:v>
       </x:c>
-      <x:c r="F34" s="15" t="str"/>
-      <x:c r="G34" t="str">
+      <x:c r="F34" s="13" t="str"/>
+      <x:c r="G34" s="13" t="str"/>
+      <x:c r="H34" s="13" t="str"/>
+      <x:c r="I34" s="13" t="str"/>
+      <x:c r="J34" s="13" t="str"/>
+      <x:c r="K34" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1024,17 +1136,21 @@
       <x:c r="B35" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C35" s="15" t="str">
+      <x:c r="C35" s="13" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="D35" s="15" t="str">
+      <x:c r="D35" s="13" t="str">
         <x:v>Incomplete, abnormal or missing data is clearly marked with remarks or justification</x:v>
       </x:c>
-      <x:c r="E35" s="15" t="str">
+      <x:c r="E35" s="13" t="str">
         <x:v>Tracker remarks column</x:v>
       </x:c>
-      <x:c r="F35" s="15" t="str"/>
-      <x:c r="G35" t="str">
+      <x:c r="F35" s="13" t="str"/>
+      <x:c r="G35" s="13" t="str"/>
+      <x:c r="H35" s="13" t="str"/>
+      <x:c r="I35" s="13" t="str"/>
+      <x:c r="J35" s="13" t="str"/>
+      <x:c r="K35" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1045,17 +1161,21 @@
       <x:c r="B36" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C36" s="15" t="str">
+      <x:c r="C36" s="13" t="str">
         <x:v>Tracker Entry and Data Submission</x:v>
       </x:c>
-      <x:c r="D36" s="15" t="str">
+      <x:c r="D36" s="13" t="str">
         <x:v>Tracker is updated within the required timeline</x:v>
       </x:c>
-      <x:c r="E36" s="15" t="str">
+      <x:c r="E36" s="13" t="str">
         <x:v>File modified date / submission email / SharePoint timestamp</x:v>
       </x:c>
-      <x:c r="F36" s="15" t="str"/>
-      <x:c r="G36" t="str">
+      <x:c r="F36" s="13" t="str"/>
+      <x:c r="G36" s="13" t="str"/>
+      <x:c r="H36" s="13" t="str"/>
+      <x:c r="I36" s="13" t="str"/>
+      <x:c r="J36" s="13" t="str"/>
+      <x:c r="K36" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1066,17 +1186,21 @@
       <x:c r="B37" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C37" s="15" t="str">
+      <x:c r="C37" s="13" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="D37" s="15" t="str">
+      <x:c r="D37" s="13" t="str">
         <x:v>Issues requiring follow-up are recorded</x:v>
       </x:c>
-      <x:c r="E37" s="15" t="str">
+      <x:c r="E37" s="13" t="str">
         <x:v>Follow-up tracker</x:v>
       </x:c>
-      <x:c r="F37" s="15" t="str"/>
-      <x:c r="G37" t="str">
+      <x:c r="F37" s="13" t="str"/>
+      <x:c r="G37" s="13" t="str"/>
+      <x:c r="H37" s="13" t="str"/>
+      <x:c r="I37" s="13" t="str"/>
+      <x:c r="J37" s="13" t="str"/>
+      <x:c r="K37" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1087,17 +1211,21 @@
       <x:c r="B38" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C38" s="15" t="str">
+      <x:c r="C38" s="13" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="D38" s="15" t="str">
+      <x:c r="D38" s="13" t="str">
         <x:v>Service Provider is notified where applicable</x:v>
       </x:c>
-      <x:c r="E38" s="15" t="str">
+      <x:c r="E38" s="13" t="str">
         <x:v>Letter / email</x:v>
       </x:c>
-      <x:c r="F38" s="15" t="str"/>
-      <x:c r="G38" t="str">
+      <x:c r="F38" s="13" t="str"/>
+      <x:c r="G38" s="13" t="str"/>
+      <x:c r="H38" s="13" t="str"/>
+      <x:c r="I38" s="13" t="str"/>
+      <x:c r="J38" s="13" t="str"/>
+      <x:c r="K38" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1108,17 +1236,21 @@
       <x:c r="B39" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C39" s="15" t="str">
+      <x:c r="C39" s="13" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="D39" s="15" t="str">
+      <x:c r="D39" s="13" t="str">
         <x:v>Reminder is issued if there is no response</x:v>
       </x:c>
-      <x:c r="E39" s="15" t="str">
+      <x:c r="E39" s="13" t="str">
         <x:v>Reminder email</x:v>
       </x:c>
-      <x:c r="F39" s="15" t="str"/>
-      <x:c r="G39" t="str">
+      <x:c r="F39" s="13" t="str"/>
+      <x:c r="G39" s="13" t="str"/>
+      <x:c r="H39" s="13" t="str"/>
+      <x:c r="I39" s="13" t="str"/>
+      <x:c r="J39" s="13" t="str"/>
+      <x:c r="K39" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1129,17 +1261,21 @@
       <x:c r="B40" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C40" s="15" t="str">
+      <x:c r="C40" s="13" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="D40" s="15" t="str">
+      <x:c r="D40" s="13" t="str">
         <x:v>Escalation is made for overdue or serious issues</x:v>
       </x:c>
-      <x:c r="E40" s="15" t="str">
+      <x:c r="E40" s="13" t="str">
         <x:v>Escalation email / management update</x:v>
       </x:c>
-      <x:c r="F40" s="15" t="str"/>
-      <x:c r="G40" t="str">
+      <x:c r="F40" s="13" t="str"/>
+      <x:c r="G40" s="13" t="str"/>
+      <x:c r="H40" s="13" t="str"/>
+      <x:c r="I40" s="13" t="str"/>
+      <x:c r="J40" s="13" t="str"/>
+      <x:c r="K40" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1150,26 +1286,30 @@
       <x:c r="B41" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C41" s="15" t="str">
+      <x:c r="C41" s="13" t="str">
         <x:v>Follow-up and Closure</x:v>
       </x:c>
-      <x:c r="D41" s="15" t="str">
+      <x:c r="D41" s="13" t="str">
         <x:v>Case is closed only when required evidence is complete</x:v>
       </x:c>
-      <x:c r="E41" s="15" t="str">
+      <x:c r="E41" s="13" t="str">
         <x:v>Closure note / final evidence</x:v>
       </x:c>
-      <x:c r="F41" s="15" t="str"/>
-      <x:c r="G41" t="str">
+      <x:c r="F41" s="13" t="str"/>
+      <x:c r="G41" s="13" t="str"/>
+      <x:c r="H41" s="13" t="str"/>
+      <x:c r="I41" s="13" t="str"/>
+      <x:c r="J41" s="13" t="str"/>
+      <x:c r="K41" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A1:K1"/>
   </x:mergeCells>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="G11:G41">
+    <x:dataValidation type="list" sqref="K11:K41">
       <x:formula1>"Yes,No"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1183,88 +1323,108 @@
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="7" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="50" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="20" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="17" t="str">
         <x:v>Audit QMOD – Repository Template</x:v>
       </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
+      <x:c r="B1" s="17"/>
+      <x:c r="C1" s="17"/>
+      <x:c r="D1" s="17"/>
+      <x:c r="E1" s="17"/>
+      <x:c r="F1" s="17"/>
+      <x:c r="G1" s="17"/>
+      <x:c r="H1" s="17"/>
+      <x:c r="I1" s="17"/>
+      <x:c r="J1" s="17"/>
+      <x:c r="K1" s="17"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="A3" s="9" t="str">
         <x:v>Template Type</x:v>
       </x:c>
-      <x:c r="B3" s="15" t="str">
+      <x:c r="B3" t="str">
         <x:v>MODULE</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>Template ID</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
+      <x:c r="B4" t="str">
         <x:v>wireless-bas</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>Template Name</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="str">
+      <x:c r="B5" t="str">
         <x:v>Wireless BAS</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="14" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>Template Version</x:v>
       </x:c>
-      <x:c r="B6" s="15" t="str">
+      <x:c r="B6" t="str">
         <x:v>1.0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="14" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>Effective Date</x:v>
       </x:c>
-      <x:c r="B7" s="15" t="str"/>
+      <x:c r="B7" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="14" t="str">
+      <x:c r="A8" s="9" t="str">
         <x:v>Source / Reference</x:v>
       </x:c>
-      <x:c r="B8" s="15" t="str"/>
+      <x:c r="B8" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="27" t="str">
+      <x:c r="A10" s="23" t="str">
         <x:v>Item ID</x:v>
       </x:c>
-      <x:c r="B10" s="27" t="str">
+      <x:c r="B10" s="23" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="str">
+      <x:c r="C10" s="23" t="str">
         <x:v>Section</x:v>
       </x:c>
-      <x:c r="D10" s="27" t="str">
+      <x:c r="D10" s="23" t="str">
         <x:v>Audit Check</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="str">
+      <x:c r="E10" s="23" t="str">
         <x:v>Evidence Expected</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="str">
+      <x:c r="F10" s="23" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G10" s="23" t="str">
+        <x:v>Evidence Link / Reference</x:v>
+      </x:c>
+      <x:c r="H10" s="23" t="str">
+        <x:v>Auditor Remark</x:v>
+      </x:c>
+      <x:c r="I10" s="23" t="str">
+        <x:v>Remark</x:v>
+      </x:c>
+      <x:c r="J10" s="23" t="str">
         <x:v>Guidance / Notes</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="str">
+      <x:c r="K10" s="23" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -1275,17 +1435,21 @@
       <x:c r="B11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="str">
+      <x:c r="C11" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="str">
+      <x:c r="D11" s="13" t="str">
         <x:v>Measurement location / area identified before field activity</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="str">
+      <x:c r="E11" s="13" t="str">
         <x:v>Planning document / location list</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="str"/>
-      <x:c r="G11" t="str">
+      <x:c r="F11" s="13" t="str"/>
+      <x:c r="G11" s="13" t="str"/>
+      <x:c r="H11" s="13" t="str"/>
+      <x:c r="I11" s="13" t="str"/>
+      <x:c r="J11" s="13" t="str"/>
+      <x:c r="K11" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1296,17 +1460,21 @@
       <x:c r="B12" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="str">
+      <x:c r="C12" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="str">
+      <x:c r="D12" s="13" t="str">
         <x:v>Complete address and coordinates are available</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="str">
+      <x:c r="E12" s="13" t="str">
         <x:v>Field form / location list / map screenshot</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="str"/>
-      <x:c r="G12" t="str">
+      <x:c r="F12" s="13" t="str"/>
+      <x:c r="G12" s="13" t="str"/>
+      <x:c r="H12" s="13" t="str"/>
+      <x:c r="I12" s="13" t="str"/>
+      <x:c r="J12" s="13" t="str"/>
+      <x:c r="K12" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1317,17 +1485,21 @@
       <x:c r="B13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="str">
+      <x:c r="C13" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="str">
+      <x:c r="D13" s="13" t="str">
         <x:v>Type of testing is clearly stated</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="str">
+      <x:c r="E13" s="13" t="str">
         <x:v>Static Test</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="str"/>
-      <x:c r="G13" t="str">
+      <x:c r="F13" s="13" t="str"/>
+      <x:c r="G13" s="13" t="str"/>
+      <x:c r="H13" s="13" t="str"/>
+      <x:c r="I13" s="13" t="str"/>
+      <x:c r="J13" s="13" t="str"/>
+      <x:c r="K13" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1338,17 +1510,21 @@
       <x:c r="B14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="str">
+      <x:c r="C14" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="str">
+      <x:c r="D14" s="13" t="str">
         <x:v>Officer in charge and team members are assigned</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="str">
+      <x:c r="E14" s="13" t="str">
         <x:v>Assignment email / task list / attendance list</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="str"/>
-      <x:c r="G14" t="str">
+      <x:c r="F14" s="13" t="str"/>
+      <x:c r="G14" s="13" t="str"/>
+      <x:c r="H14" s="13" t="str"/>
+      <x:c r="I14" s="13" t="str"/>
+      <x:c r="J14" s="13" t="str"/>
+      <x:c r="K14" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1359,17 +1535,21 @@
       <x:c r="B15" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="str">
+      <x:c r="C15" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="str">
+      <x:c r="D15" s="13" t="str">
         <x:v>Measurement date and time are planned</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="str">
+      <x:c r="E15" s="13" t="str">
         <x:v>Schedule / email / calendar / task record</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="str"/>
-      <x:c r="G15" t="str">
+      <x:c r="F15" s="13" t="str"/>
+      <x:c r="G15" s="13" t="str"/>
+      <x:c r="H15" s="13" t="str"/>
+      <x:c r="I15" s="13" t="str"/>
+      <x:c r="J15" s="13" t="str"/>
+      <x:c r="K15" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1380,17 +1560,21 @@
       <x:c r="B16" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="str">
+      <x:c r="C16" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="str">
+      <x:c r="D16" s="13" t="str">
         <x:v>Relevant MSQoS / SOP / operating manual is available to officers</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="str">
+      <x:c r="E16" s="13" t="str">
         <x:v>SOP folder screenshot / interview confirmation</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="str"/>
-      <x:c r="G16" t="str">
+      <x:c r="F16" s="13" t="str"/>
+      <x:c r="G16" s="13" t="str"/>
+      <x:c r="H16" s="13" t="str"/>
+      <x:c r="I16" s="13" t="str"/>
+      <x:c r="J16" s="13" t="str"/>
+      <x:c r="K16" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1401,17 +1585,21 @@
       <x:c r="B17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="str">
+      <x:c r="C17" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="str">
+      <x:c r="D17" s="13" t="str">
         <x:v>Equipment is prepared before measurement</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="str">
+      <x:c r="E17" s="13" t="str">
         <x:v>Equipment checklist / photo of equipment</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="str"/>
-      <x:c r="G17" t="str">
+      <x:c r="F17" s="13" t="str"/>
+      <x:c r="G17" s="13" t="str"/>
+      <x:c r="H17" s="13" t="str"/>
+      <x:c r="I17" s="13" t="str"/>
+      <x:c r="J17" s="13" t="str"/>
+      <x:c r="K17" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1422,17 +1610,21 @@
       <x:c r="B18" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="str">
+      <x:c r="C18" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="str">
+      <x:c r="D18" s="13" t="str">
         <x:v>Master unit and all slave units are available and functioning</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="str">
+      <x:c r="E18" s="13" t="str">
         <x:v>Controller View screenshot / equipment checklist</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="str"/>
-      <x:c r="G18" t="str">
+      <x:c r="F18" s="13" t="str"/>
+      <x:c r="G18" s="13" t="str"/>
+      <x:c r="H18" s="13" t="str"/>
+      <x:c r="I18" s="13" t="str"/>
+      <x:c r="J18" s="13" t="str"/>
+      <x:c r="K18" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1443,17 +1635,21 @@
       <x:c r="B19" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="str">
+      <x:c r="C19" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="str">
+      <x:c r="D19" s="13" t="str">
         <x:v>Device-to-operator mapping is verified</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="str">
+      <x:c r="E19" s="13" t="str">
         <x:v>Device mapping list</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="str"/>
-      <x:c r="G19" t="str">
+      <x:c r="F19" s="13" t="str"/>
+      <x:c r="G19" s="13" t="str"/>
+      <x:c r="H19" s="13" t="str"/>
+      <x:c r="I19" s="13" t="str"/>
+      <x:c r="J19" s="13" t="str"/>
+      <x:c r="K19" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1464,17 +1660,21 @@
       <x:c r="B20" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="str">
+      <x:c r="C20" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="str">
+      <x:c r="D20" s="13" t="str">
         <x:v>SIM cards are verified before measurement</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="str">
+      <x:c r="E20" s="13" t="str">
         <x:v>SIM list</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="str"/>
-      <x:c r="G20" t="str">
+      <x:c r="F20" s="13" t="str"/>
+      <x:c r="G20" s="13" t="str"/>
+      <x:c r="H20" s="13" t="str"/>
+      <x:c r="I20" s="13" t="str"/>
+      <x:c r="J20" s="13" t="str"/>
+      <x:c r="K20" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1485,17 +1685,21 @@
       <x:c r="B21" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="str">
+      <x:c r="C21" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="str">
+      <x:c r="D21" s="13" t="str">
         <x:v>Measurement script is prepared</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="str">
+      <x:c r="E21" s="13" t="str">
         <x:v>Script setting screenshot</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="str"/>
-      <x:c r="G21" t="str">
+      <x:c r="F21" s="13" t="str"/>
+      <x:c r="G21" s="13" t="str"/>
+      <x:c r="H21" s="13" t="str"/>
+      <x:c r="I21" s="13" t="str"/>
+      <x:c r="J21" s="13" t="str"/>
+      <x:c r="K21" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1506,17 +1710,21 @@
       <x:c r="B22" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="str">
+      <x:c r="C22" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="str">
+      <x:c r="D22" s="13" t="str">
         <x:v>Script is loaded into each slave unit</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="str">
+      <x:c r="E22" s="13" t="str">
         <x:v>Controller View screenshot showing script loaded status</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="str"/>
-      <x:c r="G22" t="str">
+      <x:c r="F22" s="13" t="str"/>
+      <x:c r="G22" s="13" t="str"/>
+      <x:c r="H22" s="13" t="str"/>
+      <x:c r="I22" s="13" t="str"/>
+      <x:c r="J22" s="13" t="str"/>
+      <x:c r="K22" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1527,17 +1735,21 @@
       <x:c r="B23" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="str">
+      <x:c r="C23" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D23" s="15" t="str">
+      <x:c r="D23" s="13" t="str">
         <x:v>Bluetooth, GPS, battery and storage are checked</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="str">
+      <x:c r="E23" s="13" t="str">
         <x:v>Device status screenshot / checklist</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="str"/>
-      <x:c r="G23" t="str">
+      <x:c r="F23" s="13" t="str"/>
+      <x:c r="G23" s="13" t="str"/>
+      <x:c r="H23" s="13" t="str"/>
+      <x:c r="I23" s="13" t="str"/>
+      <x:c r="J23" s="13" t="str"/>
+      <x:c r="K23" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1548,17 +1760,21 @@
       <x:c r="B24" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="str">
+      <x:c r="C24" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D24" s="15" t="str">
+      <x:c r="D24" s="13" t="str">
         <x:v>Pre-test trial run is conducted</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="str">
+      <x:c r="E24" s="13" t="str">
         <x:v>Trial call / short log / screenshot / field note</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="str"/>
-      <x:c r="G24" t="str">
+      <x:c r="F24" s="13" t="str"/>
+      <x:c r="G24" s="13" t="str"/>
+      <x:c r="H24" s="13" t="str"/>
+      <x:c r="I24" s="13" t="str"/>
+      <x:c r="J24" s="13" t="str"/>
+      <x:c r="K24" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1569,17 +1785,21 @@
       <x:c r="B25" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="str">
+      <x:c r="C25" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D25" s="15" t="str">
+      <x:c r="D25" s="13" t="str">
         <x:v>Measurement is conducted according to planned location</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="str">
+      <x:c r="E25" s="13" t="str">
         <x:v>Logfile map / location screenshot</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="str"/>
-      <x:c r="G25" t="str">
+      <x:c r="F25" s="13" t="str"/>
+      <x:c r="G25" s="13" t="str"/>
+      <x:c r="H25" s="13" t="str"/>
+      <x:c r="I25" s="13" t="str"/>
+      <x:c r="J25" s="13" t="str"/>
+      <x:c r="K25" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1590,17 +1810,21 @@
       <x:c r="B26" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="str">
+      <x:c r="C26" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="str">
+      <x:c r="D26" s="13" t="str">
         <x:v>Date, time and location of measurement are recorded</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="str">
+      <x:c r="E26" s="13" t="str">
         <x:v>Logfile / field form</x:v>
       </x:c>
-      <x:c r="F26" s="15" t="str"/>
-      <x:c r="G26" t="str">
+      <x:c r="F26" s="13" t="str"/>
+      <x:c r="G26" s="13" t="str"/>
+      <x:c r="H26" s="13" t="str"/>
+      <x:c r="I26" s="13" t="str"/>
+      <x:c r="J26" s="13" t="str"/>
+      <x:c r="K26" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1611,17 +1835,21 @@
       <x:c r="B27" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="str">
+      <x:c r="C27" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="str">
+      <x:c r="D27" s="13" t="str">
         <x:v>Measurement is performed using Nemo Walker Air</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="str">
+      <x:c r="E27" s="13" t="str">
         <x:v>Logfile / screenshot / field photo</x:v>
       </x:c>
-      <x:c r="F27" s="15" t="str"/>
-      <x:c r="G27" t="str">
+      <x:c r="F27" s="13" t="str"/>
+      <x:c r="G27" s="13" t="str"/>
+      <x:c r="H27" s="13" t="str"/>
+      <x:c r="I27" s="13" t="str"/>
+      <x:c r="J27" s="13" t="str"/>
+      <x:c r="K27" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1632,17 +1860,21 @@
       <x:c r="B28" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="str">
+      <x:c r="C28" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D28" s="15" t="str">
+      <x:c r="D28" s="13" t="str">
         <x:v>Correct operator sequence is used</x:v>
       </x:c>
-      <x:c r="E28" s="15" t="str">
+      <x:c r="E28" s="13" t="str">
         <x:v>Device mapping / logfile naming</x:v>
       </x:c>
-      <x:c r="F28" s="15" t="str"/>
-      <x:c r="G28" t="str">
+      <x:c r="F28" s="13" t="str"/>
+      <x:c r="G28" s="13" t="str"/>
+      <x:c r="H28" s="13" t="str"/>
+      <x:c r="I28" s="13" t="str"/>
+      <x:c r="J28" s="13" t="str"/>
+      <x:c r="K28" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1653,17 +1885,21 @@
       <x:c r="B29" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C29" s="15" t="str">
+      <x:c r="C29" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D29" s="15" t="str">
+      <x:c r="D29" s="13" t="str">
         <x:v>Correct system lock / setting is used where applicable</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="str">
+      <x:c r="E29" s="13" t="str">
         <x:v>Forcing / system lock screenshot</x:v>
       </x:c>
-      <x:c r="F29" s="15" t="str"/>
-      <x:c r="G29" t="str">
+      <x:c r="F29" s="13" t="str"/>
+      <x:c r="G29" s="13" t="str"/>
+      <x:c r="H29" s="13" t="str"/>
+      <x:c r="I29" s="13" t="str"/>
+      <x:c r="J29" s="13" t="str"/>
+      <x:c r="K29" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1674,17 +1910,21 @@
       <x:c r="B30" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C30" s="15" t="str">
+      <x:c r="C30" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D30" s="15" t="str">
+      <x:c r="D30" s="13" t="str">
         <x:v>Measurement is monitored during field activity</x:v>
       </x:c>
-      <x:c r="E30" s="15" t="str">
+      <x:c r="E30" s="13" t="str">
         <x:v>Statistics / map / controller screenshot</x:v>
       </x:c>
-      <x:c r="F30" s="15" t="str"/>
-      <x:c r="G30" t="str">
+      <x:c r="F30" s="13" t="str"/>
+      <x:c r="G30" s="13" t="str"/>
+      <x:c r="H30" s="13" t="str"/>
+      <x:c r="I30" s="13" t="str"/>
+      <x:c r="J30" s="13" t="str"/>
+      <x:c r="K30" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1695,17 +1935,21 @@
       <x:c r="B31" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C31" s="15" t="str">
+      <x:c r="C31" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D31" s="15" t="str">
+      <x:c r="D31" s="13" t="str">
         <x:v>Interruption or issue during measurement is recorded</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="str">
+      <x:c r="E31" s="13" t="str">
         <x:v>Issue log / remarks</x:v>
       </x:c>
-      <x:c r="F31" s="15" t="str"/>
-      <x:c r="G31" t="str">
+      <x:c r="F31" s="13" t="str"/>
+      <x:c r="G31" s="13" t="str"/>
+      <x:c r="H31" s="13" t="str"/>
+      <x:c r="I31" s="13" t="str"/>
+      <x:c r="J31" s="13" t="str"/>
+      <x:c r="K31" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1716,17 +1960,21 @@
       <x:c r="B32" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C32" s="15" t="str">
+      <x:c r="C32" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D32" s="15" t="str">
+      <x:c r="D32" s="13" t="str">
         <x:v>Deviation from plan is justified</x:v>
       </x:c>
-      <x:c r="E32" s="15" t="str">
+      <x:c r="E32" s="13" t="str">
         <x:v>Email / remarks / approval / justification note</x:v>
       </x:c>
-      <x:c r="F32" s="15" t="str"/>
-      <x:c r="G32" t="str">
+      <x:c r="F32" s="13" t="str"/>
+      <x:c r="G32" s="13" t="str"/>
+      <x:c r="H32" s="13" t="str"/>
+      <x:c r="I32" s="13" t="str"/>
+      <x:c r="J32" s="13" t="str"/>
+      <x:c r="K32" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1737,17 +1985,21 @@
       <x:c r="B33" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C33" s="15" t="str">
+      <x:c r="C33" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D33" s="15" t="str">
+      <x:c r="D33" s="13" t="str">
         <x:v>Logfile is saved and renamed properly</x:v>
       </x:c>
-      <x:c r="E33" s="15" t="str">
+      <x:c r="E33" s="13" t="str">
         <x:v>Logfile screenshot / folder view</x:v>
       </x:c>
-      <x:c r="F33" s="15" t="str"/>
-      <x:c r="G33" t="str">
+      <x:c r="F33" s="13" t="str"/>
+      <x:c r="G33" s="13" t="str"/>
+      <x:c r="H33" s="13" t="str"/>
+      <x:c r="I33" s="13" t="str"/>
+      <x:c r="J33" s="13" t="str"/>
+      <x:c r="K33" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1758,17 +2010,21 @@
       <x:c r="B34" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C34" s="15" t="str">
+      <x:c r="C34" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D34" s="15" t="str">
+      <x:c r="D34" s="13" t="str">
         <x:v>Logfiles are collected from slave units to master unit</x:v>
       </x:c>
-      <x:c r="E34" s="15" t="str">
+      <x:c r="E34" s="13" t="str">
         <x:v>Agent File Explorer / folder screenshot</x:v>
       </x:c>
-      <x:c r="F34" s="15" t="str"/>
-      <x:c r="G34" t="str">
+      <x:c r="F34" s="13" t="str"/>
+      <x:c r="G34" s="13" t="str"/>
+      <x:c r="H34" s="13" t="str"/>
+      <x:c r="I34" s="13" t="str"/>
+      <x:c r="J34" s="13" t="str"/>
+      <x:c r="K34" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1779,17 +2035,21 @@
       <x:c r="B35" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C35" s="15" t="str">
+      <x:c r="C35" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D35" s="15" t="str">
+      <x:c r="D35" s="13" t="str">
         <x:v>Raw logfiles are copied to official storage</x:v>
       </x:c>
-      <x:c r="E35" s="15" t="str">
+      <x:c r="E35" s="13" t="str">
         <x:v>SharePoint / official folder screenshot</x:v>
       </x:c>
-      <x:c r="F35" s="15" t="str"/>
-      <x:c r="G35" t="str">
+      <x:c r="F35" s="13" t="str"/>
+      <x:c r="G35" s="13" t="str"/>
+      <x:c r="H35" s="13" t="str"/>
+      <x:c r="I35" s="13" t="str"/>
+      <x:c r="J35" s="13" t="str"/>
+      <x:c r="K35" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1800,17 +2060,21 @@
       <x:c r="B36" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C36" s="15" t="str">
+      <x:c r="C36" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D36" s="15" t="str">
+      <x:c r="D36" s="13" t="str">
         <x:v>Logfiles are uploaded into Nemo Analyze</x:v>
       </x:c>
-      <x:c r="E36" s="15" t="str">
+      <x:c r="E36" s="13" t="str">
         <x:v>Nemo Analyze upload screenshot</x:v>
       </x:c>
-      <x:c r="F36" s="15" t="str"/>
-      <x:c r="G36" t="str">
+      <x:c r="F36" s="13" t="str"/>
+      <x:c r="G36" s="13" t="str"/>
+      <x:c r="H36" s="13" t="str"/>
+      <x:c r="I36" s="13" t="str"/>
+      <x:c r="J36" s="13" t="str"/>
+      <x:c r="K36" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1821,17 +2085,21 @@
       <x:c r="B37" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C37" s="15" t="str">
+      <x:c r="C37" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D37" s="15" t="str">
+      <x:c r="D37" s="13" t="str">
         <x:v>Logfiles are organised by folder / measurement name</x:v>
       </x:c>
-      <x:c r="E37" s="15" t="str">
+      <x:c r="E37" s="13" t="str">
         <x:v>Nemo folder / SharePoint folder</x:v>
       </x:c>
-      <x:c r="F37" s="15" t="str"/>
-      <x:c r="G37" t="str">
+      <x:c r="F37" s="13" t="str"/>
+      <x:c r="G37" s="13" t="str"/>
+      <x:c r="H37" s="13" t="str"/>
+      <x:c r="I37" s="13" t="str"/>
+      <x:c r="J37" s="13" t="str"/>
+      <x:c r="K37" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1842,17 +2110,21 @@
       <x:c r="B38" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C38" s="15" t="str">
+      <x:c r="C38" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D38" s="15" t="str">
+      <x:c r="D38" s="13" t="str">
         <x:v>Required Wireless BAS parameters are analysed</x:v>
       </x:c>
-      <x:c r="E38" s="15" t="str">
+      <x:c r="E38" s="13" t="str">
         <x:v>Analysis workbook / custom report</x:v>
       </x:c>
-      <x:c r="F38" s="15" t="str"/>
-      <x:c r="G38" t="str">
+      <x:c r="F38" s="13" t="str"/>
+      <x:c r="G38" s="13" t="str"/>
+      <x:c r="H38" s="13" t="str"/>
+      <x:c r="I38" s="13" t="str"/>
+      <x:c r="J38" s="13" t="str"/>
+      <x:c r="K38" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1863,17 +2135,21 @@
       <x:c r="B39" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C39" s="15" t="str">
+      <x:c r="C39" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D39" s="15" t="str">
+      <x:c r="D39" s="13" t="str">
         <x:v>Failed KQI is identified correctly</x:v>
       </x:c>
-      <x:c r="E39" s="15" t="str">
+      <x:c r="E39" s="13" t="str">
         <x:v>Non-compliance summary / report</x:v>
       </x:c>
-      <x:c r="F39" s="15" t="str"/>
-      <x:c r="G39" t="str">
+      <x:c r="F39" s="13" t="str"/>
+      <x:c r="G39" s="13" t="str"/>
+      <x:c r="H39" s="13" t="str"/>
+      <x:c r="I39" s="13" t="str"/>
+      <x:c r="J39" s="13" t="str"/>
+      <x:c r="K39" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1884,17 +2160,21 @@
       <x:c r="B40" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C40" s="15" t="str">
+      <x:c r="C40" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D40" s="15" t="str">
+      <x:c r="D40" s="13" t="str">
         <x:v>Result is reviewed before submission</x:v>
       </x:c>
-      <x:c r="E40" s="15" t="str">
+      <x:c r="E40" s="13" t="str">
         <x:v>Review email / sign-off / checker remarks</x:v>
       </x:c>
-      <x:c r="F40" s="15" t="str"/>
-      <x:c r="G40" t="str">
+      <x:c r="F40" s="13" t="str"/>
+      <x:c r="G40" s="13" t="str"/>
+      <x:c r="H40" s="13" t="str"/>
+      <x:c r="I40" s="13" t="str"/>
+      <x:c r="J40" s="13" t="str"/>
+      <x:c r="K40" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1905,17 +2185,21 @@
       <x:c r="B41" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C41" s="15" t="str">
+      <x:c r="C41" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D41" s="15" t="str">
+      <x:c r="D41" s="13" t="str">
         <x:v>Raw result matches submitted tracker/report</x:v>
       </x:c>
-      <x:c r="E41" s="15" t="str">
+      <x:c r="E41" s="13" t="str">
         <x:v>Sampling check between raw result, report and tracker</x:v>
       </x:c>
-      <x:c r="F41" s="15" t="str"/>
-      <x:c r="G41" t="str">
+      <x:c r="F41" s="13" t="str"/>
+      <x:c r="G41" s="13" t="str"/>
+      <x:c r="H41" s="13" t="str"/>
+      <x:c r="I41" s="13" t="str"/>
+      <x:c r="J41" s="13" t="str"/>
+      <x:c r="K41" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1926,17 +2210,21 @@
       <x:c r="B42" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C42" s="15" t="str">
+      <x:c r="C42" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D42" s="15" t="str">
+      <x:c r="D42" s="13" t="str">
         <x:v>Assumption, exclusion or limitation is documented</x:v>
       </x:c>
-      <x:c r="E42" s="15" t="str">
+      <x:c r="E42" s="13" t="str">
         <x:v>Analysis note / justification</x:v>
       </x:c>
-      <x:c r="F42" s="15" t="str"/>
-      <x:c r="G42" t="str">
+      <x:c r="F42" s="13" t="str"/>
+      <x:c r="G42" s="13" t="str"/>
+      <x:c r="H42" s="13" t="str"/>
+      <x:c r="I42" s="13" t="str"/>
+      <x:c r="J42" s="13" t="str"/>
+      <x:c r="K42" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1947,17 +2235,21 @@
       <x:c r="B43" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C43" s="15" t="str">
+      <x:c r="C43" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D43" s="15" t="str">
+      <x:c r="D43" s="13" t="str">
         <x:v>Measurement result is entered into Wireless BAS Tracker</x:v>
       </x:c>
-      <x:c r="E43" s="15" t="str">
+      <x:c r="E43" s="13" t="str">
         <x:v>Wireless BAS Tracker screenshot / system record</x:v>
       </x:c>
-      <x:c r="F43" s="15" t="str"/>
-      <x:c r="G43" t="str">
+      <x:c r="F43" s="13" t="str"/>
+      <x:c r="G43" s="13" t="str"/>
+      <x:c r="H43" s="13" t="str"/>
+      <x:c r="I43" s="13" t="str"/>
+      <x:c r="J43" s="13" t="str"/>
+      <x:c r="K43" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1968,17 +2260,21 @@
       <x:c r="B44" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C44" s="15" t="str">
+      <x:c r="C44" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D44" s="15" t="str">
+      <x:c r="D44" s="13" t="str">
         <x:v>Mandatory tracker fields are completed</x:v>
       </x:c>
-      <x:c r="E44" s="15" t="str">
+      <x:c r="E44" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F44" s="15" t="str"/>
-      <x:c r="G44" t="str">
+      <x:c r="F44" s="13" t="str"/>
+      <x:c r="G44" s="13" t="str"/>
+      <x:c r="H44" s="13" t="str"/>
+      <x:c r="I44" s="13" t="str"/>
+      <x:c r="J44" s="13" t="str"/>
+      <x:c r="K44" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -1989,17 +2285,21 @@
       <x:c r="B45" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C45" s="15" t="str">
+      <x:c r="C45" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D45" s="15" t="str">
+      <x:c r="D45" s="13" t="str">
         <x:v>Operator is selected correctly</x:v>
       </x:c>
-      <x:c r="E45" s="15" t="str">
+      <x:c r="E45" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F45" s="15" t="str"/>
-      <x:c r="G45" t="str">
+      <x:c r="F45" s="13" t="str"/>
+      <x:c r="G45" s="13" t="str"/>
+      <x:c r="H45" s="13" t="str"/>
+      <x:c r="I45" s="13" t="str"/>
+      <x:c r="J45" s="13" t="str"/>
+      <x:c r="K45" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2010,17 +2310,21 @@
       <x:c r="B46" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C46" s="15" t="str">
+      <x:c r="C46" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D46" s="15" t="str">
+      <x:c r="D46" s="13" t="str">
         <x:v>Download / upload / HTTP browsing / Youtube / Ping fields are completed</x:v>
       </x:c>
-      <x:c r="E46" s="15" t="str">
+      <x:c r="E46" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F46" s="15" t="str"/>
-      <x:c r="G46" t="str">
+      <x:c r="F46" s="13" t="str"/>
+      <x:c r="G46" s="13" t="str"/>
+      <x:c r="H46" s="13" t="str"/>
+      <x:c r="I46" s="13" t="str"/>
+      <x:c r="J46" s="13" t="str"/>
+      <x:c r="K46" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2031,17 +2335,21 @@
       <x:c r="B47" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C47" s="15" t="str">
+      <x:c r="C47" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D47" s="15" t="str">
+      <x:c r="D47" s="13" t="str">
         <x:v>Status fields are updated correctly</x:v>
       </x:c>
-      <x:c r="E47" s="15" t="str">
+      <x:c r="E47" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F47" s="15" t="str"/>
-      <x:c r="G47" t="str">
+      <x:c r="F47" s="13" t="str"/>
+      <x:c r="G47" s="13" t="str"/>
+      <x:c r="H47" s="13" t="str"/>
+      <x:c r="I47" s="13" t="str"/>
+      <x:c r="J47" s="13" t="str"/>
+      <x:c r="K47" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2052,17 +2360,21 @@
       <x:c r="B48" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C48" s="15" t="str">
+      <x:c r="C48" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D48" s="15" t="str">
+      <x:c r="D48" s="13" t="str">
         <x:v>Notice / CD status is supported by evidence</x:v>
       </x:c>
-      <x:c r="E48" s="15" t="str">
+      <x:c r="E48" s="13" t="str">
         <x:v>Tracker + report + email</x:v>
       </x:c>
-      <x:c r="F48" s="15" t="str"/>
-      <x:c r="G48" t="str">
+      <x:c r="F48" s="13" t="str"/>
+      <x:c r="G48" s="13" t="str"/>
+      <x:c r="H48" s="13" t="str"/>
+      <x:c r="I48" s="13" t="str"/>
+      <x:c r="J48" s="13" t="str"/>
+      <x:c r="K48" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2073,17 +2385,21 @@
       <x:c r="B49" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C49" s="15" t="str">
+      <x:c r="C49" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D49" s="15" t="str">
+      <x:c r="D49" s="13" t="str">
         <x:v>FIR / Notice / CD reference is filled where applicable</x:v>
       </x:c>
-      <x:c r="E49" s="15" t="str">
+      <x:c r="E49" s="13" t="str">
         <x:v>Notice / FIR / CD record</x:v>
       </x:c>
-      <x:c r="F49" s="15" t="str"/>
-      <x:c r="G49" t="str">
+      <x:c r="F49" s="13" t="str"/>
+      <x:c r="G49" s="13" t="str"/>
+      <x:c r="H49" s="13" t="str"/>
+      <x:c r="I49" s="13" t="str"/>
+      <x:c r="J49" s="13" t="str"/>
+      <x:c r="K49" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2094,17 +2410,21 @@
       <x:c r="B50" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C50" s="15" t="str">
+      <x:c r="C50" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D50" s="15" t="str">
+      <x:c r="D50" s="13" t="str">
         <x:v>MNO is notified where required</x:v>
       </x:c>
-      <x:c r="E50" s="15" t="str">
+      <x:c r="E50" s="13" t="str">
         <x:v>Email / letter</x:v>
       </x:c>
-      <x:c r="F50" s="15" t="str"/>
-      <x:c r="G50" t="str">
+      <x:c r="F50" s="13" t="str"/>
+      <x:c r="G50" s="13" t="str"/>
+      <x:c r="H50" s="13" t="str"/>
+      <x:c r="I50" s="13" t="str"/>
+      <x:c r="J50" s="13" t="str"/>
+      <x:c r="K50" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2115,17 +2435,21 @@
       <x:c r="B51" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C51" s="15" t="str">
+      <x:c r="C51" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D51" s="15" t="str">
+      <x:c r="D51" s="13" t="str">
         <x:v>Reminder is issued if MNO does not respond</x:v>
       </x:c>
-      <x:c r="E51" s="15" t="str">
+      <x:c r="E51" s="13" t="str">
         <x:v>Follow-up email</x:v>
       </x:c>
-      <x:c r="F51" s="15" t="str"/>
-      <x:c r="G51" t="str">
+      <x:c r="F51" s="13" t="str"/>
+      <x:c r="G51" s="13" t="str"/>
+      <x:c r="H51" s="13" t="str"/>
+      <x:c r="I51" s="13" t="str"/>
+      <x:c r="J51" s="13" t="str"/>
+      <x:c r="K51" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2136,26 +2460,30 @@
       <x:c r="B52" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C52" s="15" t="str">
+      <x:c r="C52" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D52" s="15" t="str">
+      <x:c r="D52" s="13" t="str">
         <x:v>Case is closed only with complete evidence</x:v>
       </x:c>
-      <x:c r="E52" s="15" t="str">
+      <x:c r="E52" s="13" t="str">
         <x:v>Closure note / final response / final tracker status</x:v>
       </x:c>
-      <x:c r="F52" s="15" t="str"/>
-      <x:c r="G52" t="str">
+      <x:c r="F52" s="13" t="str"/>
+      <x:c r="G52" s="13" t="str"/>
+      <x:c r="H52" s="13" t="str"/>
+      <x:c r="I52" s="13" t="str"/>
+      <x:c r="J52" s="13" t="str"/>
+      <x:c r="K52" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A1:K1"/>
   </x:mergeCells>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="G11:G52">
+    <x:dataValidation type="list" sqref="K11:K52">
       <x:formula1>"Yes,No"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -2169,88 +2497,108 @@
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="7" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="50" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="20" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="17" t="str">
         <x:v>Audit QMOD – Repository Template</x:v>
       </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
+      <x:c r="B1" s="17"/>
+      <x:c r="C1" s="17"/>
+      <x:c r="D1" s="17"/>
+      <x:c r="E1" s="17"/>
+      <x:c r="F1" s="17"/>
+      <x:c r="G1" s="17"/>
+      <x:c r="H1" s="17"/>
+      <x:c r="I1" s="17"/>
+      <x:c r="J1" s="17"/>
+      <x:c r="K1" s="17"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="A3" s="9" t="str">
         <x:v>Template Type</x:v>
       </x:c>
-      <x:c r="B3" s="15" t="str">
+      <x:c r="B3" t="str">
         <x:v>MODULE</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>Template ID</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
+      <x:c r="B4" t="str">
         <x:v>pcs</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>Template Name</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="str">
+      <x:c r="B5" t="str">
         <x:v>PCS</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="14" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>Template Version</x:v>
       </x:c>
-      <x:c r="B6" s="15" t="str">
+      <x:c r="B6" t="str">
         <x:v>1.0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="14" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>Effective Date</x:v>
       </x:c>
-      <x:c r="B7" s="15" t="str"/>
+      <x:c r="B7" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="14" t="str">
+      <x:c r="A8" s="9" t="str">
         <x:v>Source / Reference</x:v>
       </x:c>
-      <x:c r="B8" s="15" t="str"/>
+      <x:c r="B8" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="27" t="str">
+      <x:c r="A10" s="23" t="str">
         <x:v>Item ID</x:v>
       </x:c>
-      <x:c r="B10" s="27" t="str">
+      <x:c r="B10" s="23" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="str">
+      <x:c r="C10" s="23" t="str">
         <x:v>Section</x:v>
       </x:c>
-      <x:c r="D10" s="27" t="str">
+      <x:c r="D10" s="23" t="str">
         <x:v>Audit Check</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="str">
+      <x:c r="E10" s="23" t="str">
         <x:v>Evidence Expected</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="str">
+      <x:c r="F10" s="23" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G10" s="23" t="str">
+        <x:v>Evidence Link / Reference</x:v>
+      </x:c>
+      <x:c r="H10" s="23" t="str">
+        <x:v>Auditor Remark</x:v>
+      </x:c>
+      <x:c r="I10" s="23" t="str">
+        <x:v>Remark</x:v>
+      </x:c>
+      <x:c r="J10" s="23" t="str">
         <x:v>Guidance / Notes</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="str">
+      <x:c r="K10" s="23" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -2261,17 +2609,21 @@
       <x:c r="B11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="str">
+      <x:c r="C11" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="str">
+      <x:c r="D11" s="13" t="str">
         <x:v>Measurement location / route / area identified before field activity</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="str">
+      <x:c r="E11" s="13" t="str">
         <x:v>Planning document / route map / location list</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="str"/>
-      <x:c r="G11" t="str">
+      <x:c r="F11" s="13" t="str"/>
+      <x:c r="G11" s="13" t="str"/>
+      <x:c r="H11" s="13" t="str"/>
+      <x:c r="I11" s="13" t="str"/>
+      <x:c r="J11" s="13" t="str"/>
+      <x:c r="K11" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2282,17 +2634,21 @@
       <x:c r="B12" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="str">
+      <x:c r="C12" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="str">
+      <x:c r="D12" s="13" t="str">
         <x:v>Complete address and coordinates are available</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="str">
+      <x:c r="E12" s="13" t="str">
         <x:v>Field form / location list / map screenshot</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="str"/>
-      <x:c r="G12" t="str">
+      <x:c r="F12" s="13" t="str"/>
+      <x:c r="G12" s="13" t="str"/>
+      <x:c r="H12" s="13" t="str"/>
+      <x:c r="I12" s="13" t="str"/>
+      <x:c r="J12" s="13" t="str"/>
+      <x:c r="K12" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2303,17 +2659,21 @@
       <x:c r="B13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="str">
+      <x:c r="C13" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="str">
+      <x:c r="D13" s="13" t="str">
         <x:v>Type of testing is clearly stated</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="str">
+      <x:c r="E13" s="13" t="str">
         <x:v>Static / Drive Test</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="str"/>
-      <x:c r="G13" t="str">
+      <x:c r="F13" s="13" t="str"/>
+      <x:c r="G13" s="13" t="str"/>
+      <x:c r="H13" s="13" t="str"/>
+      <x:c r="I13" s="13" t="str"/>
+      <x:c r="J13" s="13" t="str"/>
+      <x:c r="K13" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2324,17 +2684,21 @@
       <x:c r="B14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="str">
+      <x:c r="C14" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="str">
+      <x:c r="D14" s="13" t="str">
         <x:v>Officer in charge and team members are assigned</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="str">
+      <x:c r="E14" s="13" t="str">
         <x:v>Assignment email / task list / attendance list</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="str"/>
-      <x:c r="G14" t="str">
+      <x:c r="F14" s="13" t="str"/>
+      <x:c r="G14" s="13" t="str"/>
+      <x:c r="H14" s="13" t="str"/>
+      <x:c r="I14" s="13" t="str"/>
+      <x:c r="J14" s="13" t="str"/>
+      <x:c r="K14" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2345,17 +2709,21 @@
       <x:c r="B15" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="str">
+      <x:c r="C15" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="str">
+      <x:c r="D15" s="13" t="str">
         <x:v>Measurement date and time are planned</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="str">
+      <x:c r="E15" s="13" t="str">
         <x:v>Schedule / email / calendar / task record</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="str"/>
-      <x:c r="G15" t="str">
+      <x:c r="F15" s="13" t="str"/>
+      <x:c r="G15" s="13" t="str"/>
+      <x:c r="H15" s="13" t="str"/>
+      <x:c r="I15" s="13" t="str"/>
+      <x:c r="J15" s="13" t="str"/>
+      <x:c r="K15" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2366,17 +2734,21 @@
       <x:c r="B16" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="str">
+      <x:c r="C16" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="str">
+      <x:c r="D16" s="13" t="str">
         <x:v>Relevant MSQoS / SOP / operating manual is available to officers</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="str">
+      <x:c r="E16" s="13" t="str">
         <x:v>SOP folder screenshot / interview confirmation</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="str"/>
-      <x:c r="G16" t="str">
+      <x:c r="F16" s="13" t="str"/>
+      <x:c r="G16" s="13" t="str"/>
+      <x:c r="H16" s="13" t="str"/>
+      <x:c r="I16" s="13" t="str"/>
+      <x:c r="J16" s="13" t="str"/>
+      <x:c r="K16" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2387,17 +2759,21 @@
       <x:c r="B17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="str">
+      <x:c r="C17" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="str">
+      <x:c r="D17" s="13" t="str">
         <x:v>Equipment is prepared before measurement</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="str">
+      <x:c r="E17" s="13" t="str">
         <x:v>Equipment checklist / photo of equipment</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="str"/>
-      <x:c r="G17" t="str">
+      <x:c r="F17" s="13" t="str"/>
+      <x:c r="G17" s="13" t="str"/>
+      <x:c r="H17" s="13" t="str"/>
+      <x:c r="I17" s="13" t="str"/>
+      <x:c r="J17" s="13" t="str"/>
+      <x:c r="K17" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2408,17 +2784,21 @@
       <x:c r="B18" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="str">
+      <x:c r="C18" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="str">
+      <x:c r="D18" s="13" t="str">
         <x:v>Master unit and all slave units are available and functioning</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="str">
+      <x:c r="E18" s="13" t="str">
         <x:v>Controller View screenshot / equipment checklist</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="str"/>
-      <x:c r="G18" t="str">
+      <x:c r="F18" s="13" t="str"/>
+      <x:c r="G18" s="13" t="str"/>
+      <x:c r="H18" s="13" t="str"/>
+      <x:c r="I18" s="13" t="str"/>
+      <x:c r="J18" s="13" t="str"/>
+      <x:c r="K18" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2429,17 +2809,21 @@
       <x:c r="B19" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="str">
+      <x:c r="C19" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="str">
+      <x:c r="D19" s="13" t="str">
         <x:v>Device-to-operator mapping is verified</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="str">
+      <x:c r="E19" s="13" t="str">
         <x:v>Device mapping list</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="str"/>
-      <x:c r="G19" t="str">
+      <x:c r="F19" s="13" t="str"/>
+      <x:c r="G19" s="13" t="str"/>
+      <x:c r="H19" s="13" t="str"/>
+      <x:c r="I19" s="13" t="str"/>
+      <x:c r="J19" s="13" t="str"/>
+      <x:c r="K19" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2450,17 +2834,21 @@
       <x:c r="B20" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="str">
+      <x:c r="C20" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="str">
+      <x:c r="D20" s="13" t="str">
         <x:v>SIM cards and test numbers are verified before measurement</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="str">
+      <x:c r="E20" s="13" t="str">
         <x:v>SIM list / trial call evidence / script number confirmation</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="str"/>
-      <x:c r="G20" t="str">
+      <x:c r="F20" s="13" t="str"/>
+      <x:c r="G20" s="13" t="str"/>
+      <x:c r="H20" s="13" t="str"/>
+      <x:c r="I20" s="13" t="str"/>
+      <x:c r="J20" s="13" t="str"/>
+      <x:c r="K20" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2471,17 +2859,21 @@
       <x:c r="B21" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="str">
+      <x:c r="C21" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="str">
+      <x:c r="D21" s="13" t="str">
         <x:v>Measurement script is prepared with correct voice call and wait settings</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="str">
+      <x:c r="E21" s="13" t="str">
         <x:v>Script setting screenshot</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="str"/>
-      <x:c r="G21" t="str">
+      <x:c r="F21" s="13" t="str"/>
+      <x:c r="G21" s="13" t="str"/>
+      <x:c r="H21" s="13" t="str"/>
+      <x:c r="I21" s="13" t="str"/>
+      <x:c r="J21" s="13" t="str"/>
+      <x:c r="K21" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2492,17 +2884,21 @@
       <x:c r="B22" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="str">
+      <x:c r="C22" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="str">
+      <x:c r="D22" s="13" t="str">
         <x:v>Script is loaded into each slave unit</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="str">
+      <x:c r="E22" s="13" t="str">
         <x:v>Controller View screenshot showing script loaded status</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="str"/>
-      <x:c r="G22" t="str">
+      <x:c r="F22" s="13" t="str"/>
+      <x:c r="G22" s="13" t="str"/>
+      <x:c r="H22" s="13" t="str"/>
+      <x:c r="I22" s="13" t="str"/>
+      <x:c r="J22" s="13" t="str"/>
+      <x:c r="K22" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2513,17 +2909,21 @@
       <x:c r="B23" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="str">
+      <x:c r="C23" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D23" s="15" t="str">
+      <x:c r="D23" s="13" t="str">
         <x:v>Bluetooth, GPS, battery and storage are checked</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="str">
+      <x:c r="E23" s="13" t="str">
         <x:v>Device status screenshot / checklist</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="str"/>
-      <x:c r="G23" t="str">
+      <x:c r="F23" s="13" t="str"/>
+      <x:c r="G23" s="13" t="str"/>
+      <x:c r="H23" s="13" t="str"/>
+      <x:c r="I23" s="13" t="str"/>
+      <x:c r="J23" s="13" t="str"/>
+      <x:c r="K23" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2534,17 +2934,21 @@
       <x:c r="B24" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="str">
+      <x:c r="C24" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D24" s="15" t="str">
+      <x:c r="D24" s="13" t="str">
         <x:v>Map / route is verified before start</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="str">
+      <x:c r="E24" s="13" t="str">
         <x:v>Map Workspace screenshot / route screenshot</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="str"/>
-      <x:c r="G24" t="str">
+      <x:c r="F24" s="13" t="str"/>
+      <x:c r="G24" s="13" t="str"/>
+      <x:c r="H24" s="13" t="str"/>
+      <x:c r="I24" s="13" t="str"/>
+      <x:c r="J24" s="13" t="str"/>
+      <x:c r="K24" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2555,17 +2959,21 @@
       <x:c r="B25" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="str">
+      <x:c r="C25" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D25" s="15" t="str">
+      <x:c r="D25" s="13" t="str">
         <x:v>Pre-test trial run is conducted</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="str">
+      <x:c r="E25" s="13" t="str">
         <x:v>Trial call / short log / screenshot / field note</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="str"/>
-      <x:c r="G25" t="str">
+      <x:c r="F25" s="13" t="str"/>
+      <x:c r="G25" s="13" t="str"/>
+      <x:c r="H25" s="13" t="str"/>
+      <x:c r="I25" s="13" t="str"/>
+      <x:c r="J25" s="13" t="str"/>
+      <x:c r="K25" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2576,17 +2984,21 @@
       <x:c r="B26" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="str">
+      <x:c r="C26" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="str">
+      <x:c r="D26" s="13" t="str">
         <x:v>Measurement is conducted according to planned route/location</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="str">
+      <x:c r="E26" s="13" t="str">
         <x:v>Logfile map / route screenshot</x:v>
       </x:c>
-      <x:c r="F26" s="15" t="str"/>
-      <x:c r="G26" t="str">
+      <x:c r="F26" s="13" t="str"/>
+      <x:c r="G26" s="13" t="str"/>
+      <x:c r="H26" s="13" t="str"/>
+      <x:c r="I26" s="13" t="str"/>
+      <x:c r="J26" s="13" t="str"/>
+      <x:c r="K26" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2597,17 +3009,21 @@
       <x:c r="B27" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="str">
+      <x:c r="C27" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="str">
+      <x:c r="D27" s="13" t="str">
         <x:v>Date, time and location of measurement are recorded</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="str">
+      <x:c r="E27" s="13" t="str">
         <x:v>Logfile / field form</x:v>
       </x:c>
-      <x:c r="F27" s="15" t="str"/>
-      <x:c r="G27" t="str">
+      <x:c r="F27" s="13" t="str"/>
+      <x:c r="G27" s="13" t="str"/>
+      <x:c r="H27" s="13" t="str"/>
+      <x:c r="I27" s="13" t="str"/>
+      <x:c r="J27" s="13" t="str"/>
+      <x:c r="K27" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2618,17 +3034,21 @@
       <x:c r="B28" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="str">
+      <x:c r="C28" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D28" s="15" t="str">
+      <x:c r="D28" s="13" t="str">
         <x:v>Measurement is performed using Nemo Walker Air</x:v>
       </x:c>
-      <x:c r="E28" s="15" t="str">
+      <x:c r="E28" s="13" t="str">
         <x:v>Logfile / screenshot / field photo</x:v>
       </x:c>
-      <x:c r="F28" s="15" t="str"/>
-      <x:c r="G28" t="str">
+      <x:c r="F28" s="13" t="str"/>
+      <x:c r="G28" s="13" t="str"/>
+      <x:c r="H28" s="13" t="str"/>
+      <x:c r="I28" s="13" t="str"/>
+      <x:c r="J28" s="13" t="str"/>
+      <x:c r="K28" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2639,17 +3059,21 @@
       <x:c r="B29" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C29" s="15" t="str">
+      <x:c r="C29" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D29" s="15" t="str">
+      <x:c r="D29" s="13" t="str">
         <x:v>Correct operator sequence is used</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="str">
+      <x:c r="E29" s="13" t="str">
         <x:v>Device mapping / logfile naming</x:v>
       </x:c>
-      <x:c r="F29" s="15" t="str"/>
-      <x:c r="G29" t="str">
+      <x:c r="F29" s="13" t="str"/>
+      <x:c r="G29" s="13" t="str"/>
+      <x:c r="H29" s="13" t="str"/>
+      <x:c r="I29" s="13" t="str"/>
+      <x:c r="J29" s="13" t="str"/>
+      <x:c r="K29" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2660,17 +3084,21 @@
       <x:c r="B30" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C30" s="15" t="str">
+      <x:c r="C30" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D30" s="15" t="str">
+      <x:c r="D30" s="13" t="str">
         <x:v>Correct system lock / setting is used where applicable</x:v>
       </x:c>
-      <x:c r="E30" s="15" t="str">
+      <x:c r="E30" s="13" t="str">
         <x:v>Forcing / system lock screenshot</x:v>
       </x:c>
-      <x:c r="F30" s="15" t="str"/>
-      <x:c r="G30" t="str">
+      <x:c r="F30" s="13" t="str"/>
+      <x:c r="G30" s="13" t="str"/>
+      <x:c r="H30" s="13" t="str"/>
+      <x:c r="I30" s="13" t="str"/>
+      <x:c r="J30" s="13" t="str"/>
+      <x:c r="K30" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2681,17 +3109,21 @@
       <x:c r="B31" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C31" s="15" t="str">
+      <x:c r="C31" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D31" s="15" t="str">
+      <x:c r="D31" s="13" t="str">
         <x:v>Measurement is monitored during field activity</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="str">
+      <x:c r="E31" s="13" t="str">
         <x:v>Statistics / map / controller screenshot</x:v>
       </x:c>
-      <x:c r="F31" s="15" t="str"/>
-      <x:c r="G31" t="str">
+      <x:c r="F31" s="13" t="str"/>
+      <x:c r="G31" s="13" t="str"/>
+      <x:c r="H31" s="13" t="str"/>
+      <x:c r="I31" s="13" t="str"/>
+      <x:c r="J31" s="13" t="str"/>
+      <x:c r="K31" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2702,17 +3134,21 @@
       <x:c r="B32" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C32" s="15" t="str">
+      <x:c r="C32" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D32" s="15" t="str">
+      <x:c r="D32" s="13" t="str">
         <x:v>Interruption or issue during measurement is recorded</x:v>
       </x:c>
-      <x:c r="E32" s="15" t="str">
+      <x:c r="E32" s="13" t="str">
         <x:v>Issue log / remarks</x:v>
       </x:c>
-      <x:c r="F32" s="15" t="str"/>
-      <x:c r="G32" t="str">
+      <x:c r="F32" s="13" t="str"/>
+      <x:c r="G32" s="13" t="str"/>
+      <x:c r="H32" s="13" t="str"/>
+      <x:c r="I32" s="13" t="str"/>
+      <x:c r="J32" s="13" t="str"/>
+      <x:c r="K32" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2723,17 +3159,21 @@
       <x:c r="B33" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C33" s="15" t="str">
+      <x:c r="C33" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D33" s="15" t="str">
+      <x:c r="D33" s="13" t="str">
         <x:v>Deviation from plan is justified</x:v>
       </x:c>
-      <x:c r="E33" s="15" t="str">
+      <x:c r="E33" s="13" t="str">
         <x:v>Email / remarks / approval / justification note</x:v>
       </x:c>
-      <x:c r="F33" s="15" t="str"/>
-      <x:c r="G33" t="str">
+      <x:c r="F33" s="13" t="str"/>
+      <x:c r="G33" s="13" t="str"/>
+      <x:c r="H33" s="13" t="str"/>
+      <x:c r="I33" s="13" t="str"/>
+      <x:c r="J33" s="13" t="str"/>
+      <x:c r="K33" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2744,17 +3184,21 @@
       <x:c r="B34" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C34" s="15" t="str">
+      <x:c r="C34" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D34" s="15" t="str">
+      <x:c r="D34" s="13" t="str">
         <x:v>Logfile is saved and renamed properly</x:v>
       </x:c>
-      <x:c r="E34" s="15" t="str">
+      <x:c r="E34" s="13" t="str">
         <x:v>Logfile screenshot / folder view</x:v>
       </x:c>
-      <x:c r="F34" s="15" t="str"/>
-      <x:c r="G34" t="str">
+      <x:c r="F34" s="13" t="str"/>
+      <x:c r="G34" s="13" t="str"/>
+      <x:c r="H34" s="13" t="str"/>
+      <x:c r="I34" s="13" t="str"/>
+      <x:c r="J34" s="13" t="str"/>
+      <x:c r="K34" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2765,17 +3209,21 @@
       <x:c r="B35" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C35" s="15" t="str">
+      <x:c r="C35" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D35" s="15" t="str">
+      <x:c r="D35" s="13" t="str">
         <x:v>Logfiles are collected from slave units to master unit</x:v>
       </x:c>
-      <x:c r="E35" s="15" t="str">
+      <x:c r="E35" s="13" t="str">
         <x:v>Agent File Explorer / folder screenshot</x:v>
       </x:c>
-      <x:c r="F35" s="15" t="str"/>
-      <x:c r="G35" t="str">
+      <x:c r="F35" s="13" t="str"/>
+      <x:c r="G35" s="13" t="str"/>
+      <x:c r="H35" s="13" t="str"/>
+      <x:c r="I35" s="13" t="str"/>
+      <x:c r="J35" s="13" t="str"/>
+      <x:c r="K35" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2786,17 +3234,21 @@
       <x:c r="B36" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C36" s="15" t="str">
+      <x:c r="C36" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D36" s="15" t="str">
+      <x:c r="D36" s="13" t="str">
         <x:v>Raw logfiles are copied to official storage</x:v>
       </x:c>
-      <x:c r="E36" s="15" t="str">
+      <x:c r="E36" s="13" t="str">
         <x:v>SharePoint / official folder screenshot</x:v>
       </x:c>
-      <x:c r="F36" s="15" t="str"/>
-      <x:c r="G36" t="str">
+      <x:c r="F36" s="13" t="str"/>
+      <x:c r="G36" s="13" t="str"/>
+      <x:c r="H36" s="13" t="str"/>
+      <x:c r="I36" s="13" t="str"/>
+      <x:c r="J36" s="13" t="str"/>
+      <x:c r="K36" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2807,17 +3259,21 @@
       <x:c r="B37" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C37" s="15" t="str">
+      <x:c r="C37" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D37" s="15" t="str">
+      <x:c r="D37" s="13" t="str">
         <x:v>Logfiles are uploaded into Nemo Analyze</x:v>
       </x:c>
-      <x:c r="E37" s="15" t="str">
+      <x:c r="E37" s="13" t="str">
         <x:v>Nemo Analyze upload screenshot</x:v>
       </x:c>
-      <x:c r="F37" s="15" t="str"/>
-      <x:c r="G37" t="str">
+      <x:c r="F37" s="13" t="str"/>
+      <x:c r="G37" s="13" t="str"/>
+      <x:c r="H37" s="13" t="str"/>
+      <x:c r="I37" s="13" t="str"/>
+      <x:c r="J37" s="13" t="str"/>
+      <x:c r="K37" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2828,17 +3284,21 @@
       <x:c r="B38" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C38" s="15" t="str">
+      <x:c r="C38" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D38" s="15" t="str">
+      <x:c r="D38" s="13" t="str">
         <x:v>Logfiles are organised by folder / measurement name</x:v>
       </x:c>
-      <x:c r="E38" s="15" t="str">
+      <x:c r="E38" s="13" t="str">
         <x:v>Nemo folder / SharePoint folder</x:v>
       </x:c>
-      <x:c r="F38" s="15" t="str"/>
-      <x:c r="G38" t="str">
+      <x:c r="F38" s="13" t="str"/>
+      <x:c r="G38" s="13" t="str"/>
+      <x:c r="H38" s="13" t="str"/>
+      <x:c r="I38" s="13" t="str"/>
+      <x:c r="J38" s="13" t="str"/>
+      <x:c r="K38" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2849,17 +3309,21 @@
       <x:c r="B39" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C39" s="15" t="str">
+      <x:c r="C39" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D39" s="15" t="str">
+      <x:c r="D39" s="13" t="str">
         <x:v>Required PCS parameters are analysed</x:v>
       </x:c>
-      <x:c r="E39" s="15" t="str">
+      <x:c r="E39" s="13" t="str">
         <x:v>Analysis workbook / custom report</x:v>
       </x:c>
-      <x:c r="F39" s="15" t="str"/>
-      <x:c r="G39" t="str">
+      <x:c r="F39" s="13" t="str"/>
+      <x:c r="G39" s="13" t="str"/>
+      <x:c r="H39" s="13" t="str"/>
+      <x:c r="I39" s="13" t="str"/>
+      <x:c r="J39" s="13" t="str"/>
+      <x:c r="K39" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2870,17 +3334,21 @@
       <x:c r="B40" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C40" s="15" t="str">
+      <x:c r="C40" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D40" s="15" t="str">
+      <x:c r="D40" s="13" t="str">
         <x:v>CSSR is calculated correctly</x:v>
       </x:c>
-      <x:c r="E40" s="15" t="str">
+      <x:c r="E40" s="13" t="str">
         <x:v>Analysis file / report / formula check</x:v>
       </x:c>
-      <x:c r="F40" s="15" t="str"/>
-      <x:c r="G40" t="str">
+      <x:c r="F40" s="13" t="str"/>
+      <x:c r="G40" s="13" t="str"/>
+      <x:c r="H40" s="13" t="str"/>
+      <x:c r="I40" s="13" t="str"/>
+      <x:c r="J40" s="13" t="str"/>
+      <x:c r="K40" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2891,17 +3359,21 @@
       <x:c r="B41" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C41" s="15" t="str">
+      <x:c r="C41" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D41" s="15" t="str">
+      <x:c r="D41" s="13" t="str">
         <x:v>DCR is calculated correctly</x:v>
       </x:c>
-      <x:c r="E41" s="15" t="str">
+      <x:c r="E41" s="13" t="str">
         <x:v>Analysis file / report / formula check</x:v>
       </x:c>
-      <x:c r="F41" s="15" t="str"/>
-      <x:c r="G41" t="str">
+      <x:c r="F41" s="13" t="str"/>
+      <x:c r="G41" s="13" t="str"/>
+      <x:c r="H41" s="13" t="str"/>
+      <x:c r="I41" s="13" t="str"/>
+      <x:c r="J41" s="13" t="str"/>
+      <x:c r="K41" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2912,17 +3384,21 @@
       <x:c r="B42" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C42" s="15" t="str">
+      <x:c r="C42" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D42" s="15" t="str">
+      <x:c r="D42" s="13" t="str">
         <x:v>Failed KQI is identified correctly</x:v>
       </x:c>
-      <x:c r="E42" s="15" t="str">
+      <x:c r="E42" s="13" t="str">
         <x:v>Non-compliance summary / report</x:v>
       </x:c>
-      <x:c r="F42" s="15" t="str"/>
-      <x:c r="G42" t="str">
+      <x:c r="F42" s="13" t="str"/>
+      <x:c r="G42" s="13" t="str"/>
+      <x:c r="H42" s="13" t="str"/>
+      <x:c r="I42" s="13" t="str"/>
+      <x:c r="J42" s="13" t="str"/>
+      <x:c r="K42" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2933,17 +3409,21 @@
       <x:c r="B43" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C43" s="15" t="str">
+      <x:c r="C43" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D43" s="15" t="str">
+      <x:c r="D43" s="13" t="str">
         <x:v>Result is reviewed before submission</x:v>
       </x:c>
-      <x:c r="E43" s="15" t="str">
+      <x:c r="E43" s="13" t="str">
         <x:v>Review email / sign-off / checker remarks</x:v>
       </x:c>
-      <x:c r="F43" s="15" t="str"/>
-      <x:c r="G43" t="str">
+      <x:c r="F43" s="13" t="str"/>
+      <x:c r="G43" s="13" t="str"/>
+      <x:c r="H43" s="13" t="str"/>
+      <x:c r="I43" s="13" t="str"/>
+      <x:c r="J43" s="13" t="str"/>
+      <x:c r="K43" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2954,17 +3434,21 @@
       <x:c r="B44" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C44" s="15" t="str">
+      <x:c r="C44" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D44" s="15" t="str">
+      <x:c r="D44" s="13" t="str">
         <x:v>Raw result matches submitted tracker/report</x:v>
       </x:c>
-      <x:c r="E44" s="15" t="str">
+      <x:c r="E44" s="13" t="str">
         <x:v>Sampling check between raw result, report and tracker</x:v>
       </x:c>
-      <x:c r="F44" s="15" t="str"/>
-      <x:c r="G44" t="str">
+      <x:c r="F44" s="13" t="str"/>
+      <x:c r="G44" s="13" t="str"/>
+      <x:c r="H44" s="13" t="str"/>
+      <x:c r="I44" s="13" t="str"/>
+      <x:c r="J44" s="13" t="str"/>
+      <x:c r="K44" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2975,17 +3459,21 @@
       <x:c r="B45" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C45" s="15" t="str">
+      <x:c r="C45" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D45" s="15" t="str">
+      <x:c r="D45" s="13" t="str">
         <x:v>Assumption, exclusion or limitation is documented</x:v>
       </x:c>
-      <x:c r="E45" s="15" t="str">
+      <x:c r="E45" s="13" t="str">
         <x:v>Analysis note / justification</x:v>
       </x:c>
-      <x:c r="F45" s="15" t="str"/>
-      <x:c r="G45" t="str">
+      <x:c r="F45" s="13" t="str"/>
+      <x:c r="G45" s="13" t="str"/>
+      <x:c r="H45" s="13" t="str"/>
+      <x:c r="I45" s="13" t="str"/>
+      <x:c r="J45" s="13" t="str"/>
+      <x:c r="K45" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -2996,17 +3484,21 @@
       <x:c r="B46" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C46" s="15" t="str">
+      <x:c r="C46" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D46" s="15" t="str">
+      <x:c r="D46" s="13" t="str">
         <x:v>Measurement result is entered into PCS Tracker</x:v>
       </x:c>
-      <x:c r="E46" s="15" t="str">
+      <x:c r="E46" s="13" t="str">
         <x:v>PCS Tracker screenshot / system record</x:v>
       </x:c>
-      <x:c r="F46" s="15" t="str"/>
-      <x:c r="G46" t="str">
+      <x:c r="F46" s="13" t="str"/>
+      <x:c r="G46" s="13" t="str"/>
+      <x:c r="H46" s="13" t="str"/>
+      <x:c r="I46" s="13" t="str"/>
+      <x:c r="J46" s="13" t="str"/>
+      <x:c r="K46" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3017,17 +3509,21 @@
       <x:c r="B47" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C47" s="15" t="str">
+      <x:c r="C47" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D47" s="15" t="str">
+      <x:c r="D47" s="13" t="str">
         <x:v>Mandatory tracker fields are completed</x:v>
       </x:c>
-      <x:c r="E47" s="15" t="str">
+      <x:c r="E47" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F47" s="15" t="str"/>
-      <x:c r="G47" t="str">
+      <x:c r="F47" s="13" t="str"/>
+      <x:c r="G47" s="13" t="str"/>
+      <x:c r="H47" s="13" t="str"/>
+      <x:c r="I47" s="13" t="str"/>
+      <x:c r="J47" s="13" t="str"/>
+      <x:c r="K47" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3038,17 +3534,21 @@
       <x:c r="B48" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C48" s="15" t="str">
+      <x:c r="C48" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D48" s="15" t="str">
+      <x:c r="D48" s="13" t="str">
         <x:v>Operator is selected correctly</x:v>
       </x:c>
-      <x:c r="E48" s="15" t="str">
+      <x:c r="E48" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F48" s="15" t="str"/>
-      <x:c r="G48" t="str">
+      <x:c r="F48" s="13" t="str"/>
+      <x:c r="G48" s="13" t="str"/>
+      <x:c r="H48" s="13" t="str"/>
+      <x:c r="I48" s="13" t="str"/>
+      <x:c r="J48" s="13" t="str"/>
+      <x:c r="K48" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3059,17 +3559,21 @@
       <x:c r="B49" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C49" s="15" t="str">
+      <x:c r="C49" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D49" s="15" t="str">
+      <x:c r="D49" s="13" t="str">
         <x:v>CSSR / DCR / Call Attempt / Drop fields are completed</x:v>
       </x:c>
-      <x:c r="E49" s="15" t="str">
+      <x:c r="E49" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F49" s="15" t="str"/>
-      <x:c r="G49" t="str">
+      <x:c r="F49" s="13" t="str"/>
+      <x:c r="G49" s="13" t="str"/>
+      <x:c r="H49" s="13" t="str"/>
+      <x:c r="I49" s="13" t="str"/>
+      <x:c r="J49" s="13" t="str"/>
+      <x:c r="K49" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3080,17 +3584,21 @@
       <x:c r="B50" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C50" s="15" t="str">
+      <x:c r="C50" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D50" s="15" t="str">
+      <x:c r="D50" s="13" t="str">
         <x:v>Status CSSR and Status Drop are updated correctly</x:v>
       </x:c>
-      <x:c r="E50" s="15" t="str">
+      <x:c r="E50" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F50" s="15" t="str"/>
-      <x:c r="G50" t="str">
+      <x:c r="F50" s="13" t="str"/>
+      <x:c r="G50" s="13" t="str"/>
+      <x:c r="H50" s="13" t="str"/>
+      <x:c r="I50" s="13" t="str"/>
+      <x:c r="J50" s="13" t="str"/>
+      <x:c r="K50" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3101,17 +3609,21 @@
       <x:c r="B51" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C51" s="15" t="str">
+      <x:c r="C51" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D51" s="15" t="str">
+      <x:c r="D51" s="13" t="str">
         <x:v>Notice / CD status is supported by evidence</x:v>
       </x:c>
-      <x:c r="E51" s="15" t="str">
+      <x:c r="E51" s="13" t="str">
         <x:v>Tracker + report + email</x:v>
       </x:c>
-      <x:c r="F51" s="15" t="str"/>
-      <x:c r="G51" t="str">
+      <x:c r="F51" s="13" t="str"/>
+      <x:c r="G51" s="13" t="str"/>
+      <x:c r="H51" s="13" t="str"/>
+      <x:c r="I51" s="13" t="str"/>
+      <x:c r="J51" s="13" t="str"/>
+      <x:c r="K51" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3122,17 +3634,21 @@
       <x:c r="B52" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C52" s="15" t="str">
+      <x:c r="C52" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D52" s="15" t="str">
+      <x:c r="D52" s="13" t="str">
         <x:v>FIR / Notice / CD reference is filled where applicable</x:v>
       </x:c>
-      <x:c r="E52" s="15" t="str">
+      <x:c r="E52" s="13" t="str">
         <x:v>Notice / FIR / CD record</x:v>
       </x:c>
-      <x:c r="F52" s="15" t="str"/>
-      <x:c r="G52" t="str">
+      <x:c r="F52" s="13" t="str"/>
+      <x:c r="G52" s="13" t="str"/>
+      <x:c r="H52" s="13" t="str"/>
+      <x:c r="I52" s="13" t="str"/>
+      <x:c r="J52" s="13" t="str"/>
+      <x:c r="K52" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3143,17 +3659,21 @@
       <x:c r="B53" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C53" s="15" t="str">
+      <x:c r="C53" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D53" s="15" t="str">
+      <x:c r="D53" s="13" t="str">
         <x:v>MNO is notified where required</x:v>
       </x:c>
-      <x:c r="E53" s="15" t="str">
+      <x:c r="E53" s="13" t="str">
         <x:v>Email / letter</x:v>
       </x:c>
-      <x:c r="F53" s="15" t="str"/>
-      <x:c r="G53" t="str">
+      <x:c r="F53" s="13" t="str"/>
+      <x:c r="G53" s="13" t="str"/>
+      <x:c r="H53" s="13" t="str"/>
+      <x:c r="I53" s="13" t="str"/>
+      <x:c r="J53" s="13" t="str"/>
+      <x:c r="K53" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3164,17 +3684,21 @@
       <x:c r="B54" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C54" s="15" t="str">
+      <x:c r="C54" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D54" s="15" t="str">
+      <x:c r="D54" s="13" t="str">
         <x:v>Reminder is issued if MNO does not respond</x:v>
       </x:c>
-      <x:c r="E54" s="15" t="str">
+      <x:c r="E54" s="13" t="str">
         <x:v>Follow-up email</x:v>
       </x:c>
-      <x:c r="F54" s="15" t="str"/>
-      <x:c r="G54" t="str">
+      <x:c r="F54" s="13" t="str"/>
+      <x:c r="G54" s="13" t="str"/>
+      <x:c r="H54" s="13" t="str"/>
+      <x:c r="I54" s="13" t="str"/>
+      <x:c r="J54" s="13" t="str"/>
+      <x:c r="K54" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3185,26 +3709,30 @@
       <x:c r="B55" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C55" s="15" t="str">
+      <x:c r="C55" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D55" s="15" t="str">
+      <x:c r="D55" s="13" t="str">
         <x:v>Case is closed only with complete evidence</x:v>
       </x:c>
-      <x:c r="E55" s="15" t="str">
+      <x:c r="E55" s="13" t="str">
         <x:v>Closure note / final response / final tracker status</x:v>
       </x:c>
-      <x:c r="F55" s="15" t="str"/>
-      <x:c r="G55" t="str">
+      <x:c r="F55" s="13" t="str"/>
+      <x:c r="G55" s="13" t="str"/>
+      <x:c r="H55" s="13" t="str"/>
+      <x:c r="I55" s="13" t="str"/>
+      <x:c r="J55" s="13" t="str"/>
+      <x:c r="K55" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A1:K1"/>
   </x:mergeCells>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="G11:G55">
+    <x:dataValidation type="list" sqref="K11:K55">
       <x:formula1>"Yes,No"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -3218,88 +3746,108 @@
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="7" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="32" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="50" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="20" t="str">
+    <x:row r="1">
+      <x:c r="A1" s="17" t="str">
         <x:v>Audit QMOD – Repository Template</x:v>
       </x:c>
-      <x:c r="B1" s="20"/>
-      <x:c r="C1" s="20"/>
-      <x:c r="D1" s="20"/>
-      <x:c r="E1" s="20"/>
-      <x:c r="F1" s="20"/>
-      <x:c r="G1" s="20"/>
+      <x:c r="B1" s="17"/>
+      <x:c r="C1" s="17"/>
+      <x:c r="D1" s="17"/>
+      <x:c r="E1" s="17"/>
+      <x:c r="F1" s="17"/>
+      <x:c r="G1" s="17"/>
+      <x:c r="H1" s="17"/>
+      <x:c r="I1" s="17"/>
+      <x:c r="J1" s="17"/>
+      <x:c r="K1" s="17"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="A3" s="9" t="str">
         <x:v>Template Type</x:v>
       </x:c>
-      <x:c r="B3" s="15" t="str">
+      <x:c r="B3" t="str">
         <x:v>MODULE</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>Template ID</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
+      <x:c r="B4" t="str">
         <x:v>wired-bas</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="14" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>Template Name</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="str">
+      <x:c r="B5" t="str">
         <x:v>Wired BAS</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="14" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>Template Version</x:v>
       </x:c>
-      <x:c r="B6" s="15" t="str">
+      <x:c r="B6" t="str">
         <x:v>1.0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="14" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>Effective Date</x:v>
       </x:c>
-      <x:c r="B7" s="15" t="str"/>
+      <x:c r="B7" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="14" t="str">
+      <x:c r="A8" s="9" t="str">
         <x:v>Source / Reference</x:v>
       </x:c>
-      <x:c r="B8" s="15" t="str"/>
+      <x:c r="B8" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="27" t="str">
+      <x:c r="A10" s="23" t="str">
         <x:v>Item ID</x:v>
       </x:c>
-      <x:c r="B10" s="27" t="str">
+      <x:c r="B10" s="23" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="C10" s="27" t="str">
+      <x:c r="C10" s="23" t="str">
         <x:v>Section</x:v>
       </x:c>
-      <x:c r="D10" s="27" t="str">
+      <x:c r="D10" s="23" t="str">
         <x:v>Audit Check</x:v>
       </x:c>
-      <x:c r="E10" s="27" t="str">
+      <x:c r="E10" s="23" t="str">
         <x:v>Evidence Expected</x:v>
       </x:c>
-      <x:c r="F10" s="27" t="str">
+      <x:c r="F10" s="23" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G10" s="23" t="str">
+        <x:v>Evidence Link / Reference</x:v>
+      </x:c>
+      <x:c r="H10" s="23" t="str">
+        <x:v>Auditor Remark</x:v>
+      </x:c>
+      <x:c r="I10" s="23" t="str">
+        <x:v>Remark</x:v>
+      </x:c>
+      <x:c r="J10" s="23" t="str">
         <x:v>Guidance / Notes</x:v>
       </x:c>
-      <x:c r="G10" s="27" t="str">
+      <x:c r="K10" s="23" t="str">
         <x:v>Active</x:v>
       </x:c>
     </x:row>
@@ -3310,17 +3858,21 @@
       <x:c r="B11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="str">
+      <x:c r="C11" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="str">
+      <x:c r="D11" s="13" t="str">
         <x:v>Premise or measurement location is identified before field activity</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="str">
+      <x:c r="E11" s="13" t="str">
         <x:v>Planning document / premise or measurement location list</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="str"/>
-      <x:c r="G11" t="str">
+      <x:c r="F11" s="13" t="str"/>
+      <x:c r="G11" s="13" t="str"/>
+      <x:c r="H11" s="13" t="str"/>
+      <x:c r="I11" s="13" t="str"/>
+      <x:c r="J11" s="13" t="str"/>
+      <x:c r="K11" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3331,17 +3883,21 @@
       <x:c r="B12" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="str">
+      <x:c r="C12" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D12" s="15" t="str">
+      <x:c r="D12" s="13" t="str">
         <x:v>Premise or measurement location complete address and coordinates are available</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="str">
+      <x:c r="E12" s="13" t="str">
         <x:v>premise or measurement location list / map screenshot</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="str"/>
-      <x:c r="G12" t="str">
+      <x:c r="F12" s="13" t="str"/>
+      <x:c r="G12" s="13" t="str"/>
+      <x:c r="H12" s="13" t="str"/>
+      <x:c r="I12" s="13" t="str"/>
+      <x:c r="J12" s="13" t="str"/>
+      <x:c r="K12" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3352,17 +3908,21 @@
       <x:c r="B13" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="str">
+      <x:c r="C13" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="str">
+      <x:c r="D13" s="13" t="str">
         <x:v>Officer in charge and team members are assigned</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="str">
+      <x:c r="E13" s="13" t="str">
         <x:v>Assignment email / task list / attendance list</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="str"/>
-      <x:c r="G13" t="str">
+      <x:c r="F13" s="13" t="str"/>
+      <x:c r="G13" s="13" t="str"/>
+      <x:c r="H13" s="13" t="str"/>
+      <x:c r="I13" s="13" t="str"/>
+      <x:c r="J13" s="13" t="str"/>
+      <x:c r="K13" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3373,17 +3933,21 @@
       <x:c r="B14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="str">
+      <x:c r="C14" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="str">
+      <x:c r="D14" s="13" t="str">
         <x:v>Measurement date and time are planned</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="str">
+      <x:c r="E14" s="13" t="str">
         <x:v>Schedule / email / calendar / task record</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="str"/>
-      <x:c r="G14" t="str">
+      <x:c r="F14" s="13" t="str"/>
+      <x:c r="G14" s="13" t="str"/>
+      <x:c r="H14" s="13" t="str"/>
+      <x:c r="I14" s="13" t="str"/>
+      <x:c r="J14" s="13" t="str"/>
+      <x:c r="K14" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3394,17 +3958,21 @@
       <x:c r="B15" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="str">
+      <x:c r="C15" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="str">
+      <x:c r="D15" s="13" t="str">
         <x:v>Relevant MSQoS / SOP / operating manual is available to officers</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="str">
+      <x:c r="E15" s="13" t="str">
         <x:v>SOP folder screenshot / interview confirmation</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="str"/>
-      <x:c r="G15" t="str">
+      <x:c r="F15" s="13" t="str"/>
+      <x:c r="G15" s="13" t="str"/>
+      <x:c r="H15" s="13" t="str"/>
+      <x:c r="I15" s="13" t="str"/>
+      <x:c r="J15" s="13" t="str"/>
+      <x:c r="K15" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3415,17 +3983,21 @@
       <x:c r="B16" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="str">
+      <x:c r="C16" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="str">
+      <x:c r="D16" s="13" t="str">
         <x:v>Get the permission from the premise owner by signing the notice to enter premise prior to the measurement</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="str">
+      <x:c r="E16" s="13" t="str">
         <x:v>Picture of the signed notice to enter premise</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="str"/>
-      <x:c r="G16" t="str">
+      <x:c r="F16" s="13" t="str"/>
+      <x:c r="G16" s="13" t="str"/>
+      <x:c r="H16" s="13" t="str"/>
+      <x:c r="I16" s="13" t="str"/>
+      <x:c r="J16" s="13" t="str"/>
+      <x:c r="K16" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3436,17 +4008,21 @@
       <x:c r="B17" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="str">
+      <x:c r="C17" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="str">
+      <x:c r="D17" s="13" t="str">
         <x:v>Photographs of measurement tools evidence are taken prior to the measurement session</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="str">
+      <x:c r="E17" s="13" t="str">
         <x:v>Equipment checklist / photo of equipment tools</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="str"/>
-      <x:c r="G17" t="str">
+      <x:c r="F17" s="13" t="str"/>
+      <x:c r="G17" s="13" t="str"/>
+      <x:c r="H17" s="13" t="str"/>
+      <x:c r="I17" s="13" t="str"/>
+      <x:c r="J17" s="13" t="str"/>
+      <x:c r="K17" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3457,17 +4033,21 @@
       <x:c r="B18" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="str">
+      <x:c r="C18" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D18" s="15" t="str">
+      <x:c r="D18" s="13" t="str">
         <x:v>Photographs of network equipment evidence such as modem routers are taken prior to the measurement session</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="str">
+      <x:c r="E18" s="13" t="str">
         <x:v>Photo of modem routers</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="str"/>
-      <x:c r="G18" t="str">
+      <x:c r="F18" s="13" t="str"/>
+      <x:c r="G18" s="13" t="str"/>
+      <x:c r="H18" s="13" t="str"/>
+      <x:c r="I18" s="13" t="str"/>
+      <x:c r="J18" s="13" t="str"/>
+      <x:c r="K18" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3478,17 +4058,21 @@
       <x:c r="B19" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="str">
+      <x:c r="C19" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="str">
+      <x:c r="D19" s="13" t="str">
         <x:v>The officer in charge is able to identify and use the original CAT 6 or higher variant cable during the measurement process</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="str">
+      <x:c r="E19" s="13" t="str">
         <x:v>Photo of CAT 6 or higher variant cable</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="str"/>
-      <x:c r="G19" t="str">
+      <x:c r="F19" s="13" t="str"/>
+      <x:c r="G19" s="13" t="str"/>
+      <x:c r="H19" s="13" t="str"/>
+      <x:c r="I19" s="13" t="str"/>
+      <x:c r="J19" s="13" t="str"/>
+      <x:c r="K19" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3499,17 +4083,21 @@
       <x:c r="B20" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="str">
+      <x:c r="C20" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D20" s="15" t="str">
+      <x:c r="D20" s="13" t="str">
         <x:v>Able to log in into the EXFOWorx website by using valid credentials</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="str">
+      <x:c r="E20" s="13" t="str">
         <x:v>EXFOWorx View screenshot</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="str"/>
-      <x:c r="G20" t="str">
+      <x:c r="F20" s="13" t="str"/>
+      <x:c r="G20" s="13" t="str"/>
+      <x:c r="H20" s="13" t="str"/>
+      <x:c r="I20" s="13" t="str"/>
+      <x:c r="J20" s="13" t="str"/>
+      <x:c r="K20" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3520,17 +4108,21 @@
       <x:c r="B21" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="str">
+      <x:c r="C21" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D21" s="15" t="str">
+      <x:c r="D21" s="13" t="str">
         <x:v>The Command Prompt/ Command Line Interface (CLI) is functioning properly and can execute Linux commands effectively</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="str">
+      <x:c r="E21" s="13" t="str">
         <x:v>Screenshot on Linux executed command in Command Prompt</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="str"/>
-      <x:c r="G21" t="str">
+      <x:c r="F21" s="13" t="str"/>
+      <x:c r="G21" s="13" t="str"/>
+      <x:c r="H21" s="13" t="str"/>
+      <x:c r="I21" s="13" t="str"/>
+      <x:c r="J21" s="13" t="str"/>
+      <x:c r="K21" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3541,21 +4133,25 @@
       <x:c r="B22" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="str">
+      <x:c r="C22" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="str">
+      <x:c r="D22" s="13" t="str">
         <x:v>Services template is prepared with correct parameter settings
 i) targeted server
 ii) type of test conducted
 iii) user credentials
 iv) the file size</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="str">
+      <x:c r="E22" s="13" t="str">
         <x:v>Services template screenshot</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="str"/>
-      <x:c r="G22" t="str">
+      <x:c r="F22" s="13" t="str"/>
+      <x:c r="G22" s="13" t="str"/>
+      <x:c r="H22" s="13" t="str"/>
+      <x:c r="I22" s="13" t="str"/>
+      <x:c r="J22" s="13" t="str"/>
+      <x:c r="K22" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3566,17 +4162,21 @@
       <x:c r="B23" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="str">
+      <x:c r="C23" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D23" s="15" t="str">
+      <x:c r="D23" s="13" t="str">
         <x:v>SLA template is prepared with the correct verifier and service to use</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="str">
+      <x:c r="E23" s="13" t="str">
         <x:v>SLA template screenshot</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="str"/>
-      <x:c r="G23" t="str">
+      <x:c r="F23" s="13" t="str"/>
+      <x:c r="G23" s="13" t="str"/>
+      <x:c r="H23" s="13" t="str"/>
+      <x:c r="I23" s="13" t="str"/>
+      <x:c r="J23" s="13" t="str"/>
+      <x:c r="K23" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3587,10 +4187,10 @@
       <x:c r="B24" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="str">
+      <x:c r="C24" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D24" s="15" t="str">
+      <x:c r="D24" s="13" t="str">
         <x:v>Report template is prepared with the correct parameter settings
 i) Data source
 ii) SLAs
@@ -3601,11 +4201,15 @@
 vii) Display Method
 viii) Report Title</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="str">
+      <x:c r="E24" s="13" t="str">
         <x:v>Reports Template Screenshot</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="str"/>
-      <x:c r="G24" t="str">
+      <x:c r="F24" s="13" t="str"/>
+      <x:c r="G24" s="13" t="str"/>
+      <x:c r="H24" s="13" t="str"/>
+      <x:c r="I24" s="13" t="str"/>
+      <x:c r="J24" s="13" t="str"/>
+      <x:c r="K24" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3616,17 +4220,21 @@
       <x:c r="B25" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="str">
+      <x:c r="C25" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D25" s="15" t="str">
+      <x:c r="D25" s="13" t="str">
         <x:v>Ensure the Residential Gateway (RG) Wi-Fi function is fully disabled before the test starts</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="str">
+      <x:c r="E25" s="13" t="str">
         <x:v>Screenshot of the SP's website to disable the Wi-Fi function</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="str"/>
-      <x:c r="G25" t="str">
+      <x:c r="F25" s="13" t="str"/>
+      <x:c r="G25" s="13" t="str"/>
+      <x:c r="H25" s="13" t="str"/>
+      <x:c r="I25" s="13" t="str"/>
+      <x:c r="J25" s="13" t="str"/>
+      <x:c r="K25" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3637,17 +4245,21 @@
       <x:c r="B26" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="str">
+      <x:c r="C26" s="13" t="str">
         <x:v>A. Pre-Measurement Preparation</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="str">
+      <x:c r="D26" s="13" t="str">
         <x:v>Ensure the Residential Gateway (RG) / router was rebooted before the test starts</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="str">
+      <x:c r="E26" s="13" t="str">
         <x:v>Evidence photo on the rebooting process of the RG / router</x:v>
       </x:c>
-      <x:c r="F26" s="15" t="str"/>
-      <x:c r="G26" t="str">
+      <x:c r="F26" s="13" t="str"/>
+      <x:c r="G26" s="13" t="str"/>
+      <x:c r="H26" s="13" t="str"/>
+      <x:c r="I26" s="13" t="str"/>
+      <x:c r="J26" s="13" t="str"/>
+      <x:c r="K26" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3658,17 +4270,21 @@
       <x:c r="B27" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="str">
+      <x:c r="C27" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="str">
+      <x:c r="D27" s="13" t="str">
         <x:v>Able to display the device name, server communication settings and server discovery settings from the CLI.</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="str">
+      <x:c r="E27" s="13" t="str">
         <x:v>Screenshot on the successful executed Linux commands from Command Prompt</x:v>
       </x:c>
-      <x:c r="F27" s="15" t="str"/>
-      <x:c r="G27" t="str">
+      <x:c r="F27" s="13" t="str"/>
+      <x:c r="G27" s="13" t="str"/>
+      <x:c r="H27" s="13" t="str"/>
+      <x:c r="I27" s="13" t="str"/>
+      <x:c r="J27" s="13" t="str"/>
+      <x:c r="K27" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3679,17 +4295,21 @@
       <x:c r="B28" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="str">
+      <x:c r="C28" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D28" s="15" t="str">
+      <x:c r="D28" s="13" t="str">
         <x:v>Ping command returns to a successful response from EXFO EVA</x:v>
       </x:c>
-      <x:c r="E28" s="15" t="str">
+      <x:c r="E28" s="13" t="str">
         <x:v>Screenshot on the successful ping command response from Command Prompt</x:v>
       </x:c>
-      <x:c r="F28" s="15" t="str"/>
-      <x:c r="G28" t="str">
+      <x:c r="F28" s="13" t="str"/>
+      <x:c r="G28" s="13" t="str"/>
+      <x:c r="H28" s="13" t="str"/>
+      <x:c r="I28" s="13" t="str"/>
+      <x:c r="J28" s="13" t="str"/>
+      <x:c r="K28" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3700,17 +4320,21 @@
       <x:c r="B29" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C29" s="15" t="str">
+      <x:c r="C29" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D29" s="15" t="str">
+      <x:c r="D29" s="13" t="str">
         <x:v>Able to log in to the EXFO BrixWorx system via SSH using valid credentials</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="str">
+      <x:c r="E29" s="13" t="str">
         <x:v>Screenshot showing the successful execution of an SSH command in the Command Prompt to access the EXFO BrixWorx system</x:v>
       </x:c>
-      <x:c r="F29" s="15" t="str"/>
-      <x:c r="G29" t="str">
+      <x:c r="F29" s="13" t="str"/>
+      <x:c r="G29" s="13" t="str"/>
+      <x:c r="H29" s="13" t="str"/>
+      <x:c r="I29" s="13" t="str"/>
+      <x:c r="J29" s="13" t="str"/>
+      <x:c r="K29" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3721,17 +4345,21 @@
       <x:c r="B30" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C30" s="15" t="str">
+      <x:c r="C30" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D30" s="15" t="str">
+      <x:c r="D30" s="13" t="str">
         <x:v>Able to check the network card status of EXFO BrixWorx</x:v>
       </x:c>
-      <x:c r="E30" s="15" t="str">
+      <x:c r="E30" s="13" t="str">
         <x:v>Screenshot on the successful execution of an SSH command to check the network card status of EXFO BrixWorx system</x:v>
       </x:c>
-      <x:c r="F30" s="15" t="str"/>
-      <x:c r="G30" t="str">
+      <x:c r="F30" s="13" t="str"/>
+      <x:c r="G30" s="13" t="str"/>
+      <x:c r="H30" s="13" t="str"/>
+      <x:c r="I30" s="13" t="str"/>
+      <x:c r="J30" s="13" t="str"/>
+      <x:c r="K30" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3742,17 +4370,21 @@
       <x:c r="B31" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C31" s="15" t="str">
+      <x:c r="C31" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D31" s="15" t="str">
+      <x:c r="D31" s="13" t="str">
         <x:v>Able to check the EXFO BrixWorx connectivity</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="str">
+      <x:c r="E31" s="13" t="str">
         <x:v>Screenshot on the successful execution of an SSH command to check the connectivity status of EXFO BrixWorx system</x:v>
       </x:c>
-      <x:c r="F31" s="15" t="str"/>
-      <x:c r="G31" t="str">
+      <x:c r="F31" s="13" t="str"/>
+      <x:c r="G31" s="13" t="str"/>
+      <x:c r="H31" s="13" t="str"/>
+      <x:c r="I31" s="13" t="str"/>
+      <x:c r="J31" s="13" t="str"/>
+      <x:c r="K31" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3763,17 +4395,21 @@
       <x:c r="B32" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C32" s="15" t="str">
+      <x:c r="C32" s="13" t="str">
         <x:v>B. Measurement Execution</x:v>
       </x:c>
-      <x:c r="D32" s="15" t="str">
+      <x:c r="D32" s="13" t="str">
         <x:v>Able to save and display the report in order to view the measurement report after creating the Report template</x:v>
       </x:c>
-      <x:c r="E32" s="15" t="str">
+      <x:c r="E32" s="13" t="str">
         <x:v>Screenshot displaying the successful measurement results report</x:v>
       </x:c>
-      <x:c r="F32" s="15" t="str"/>
-      <x:c r="G32" t="str">
+      <x:c r="F32" s="13" t="str"/>
+      <x:c r="G32" s="13" t="str"/>
+      <x:c r="H32" s="13" t="str"/>
+      <x:c r="I32" s="13" t="str"/>
+      <x:c r="J32" s="13" t="str"/>
+      <x:c r="K32" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3784,17 +4420,21 @@
       <x:c r="B33" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C33" s="15" t="str">
+      <x:c r="C33" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D33" s="15" t="str">
+      <x:c r="D33" s="13" t="str">
         <x:v>CSV measurement report is able to download</x:v>
       </x:c>
-      <x:c r="E33" s="15" t="str">
+      <x:c r="E33" s="13" t="str">
         <x:v>Screenshot of CSV measurement report</x:v>
       </x:c>
-      <x:c r="F33" s="15" t="str"/>
-      <x:c r="G33" t="str">
+      <x:c r="F33" s="13" t="str"/>
+      <x:c r="G33" s="13" t="str"/>
+      <x:c r="H33" s="13" t="str"/>
+      <x:c r="I33" s="13" t="str"/>
+      <x:c r="J33" s="13" t="str"/>
+      <x:c r="K33" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3805,17 +4445,21 @@
       <x:c r="B34" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C34" s="15" t="str">
+      <x:c r="C34" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D34" s="15" t="str">
+      <x:c r="D34" s="13" t="str">
         <x:v>Deactive the SLA once the measurement has completed</x:v>
       </x:c>
-      <x:c r="E34" s="15" t="str">
+      <x:c r="E34" s="13" t="str">
         <x:v>Screenshot of the deactivation of SLA</x:v>
       </x:c>
-      <x:c r="F34" s="15" t="str"/>
-      <x:c r="G34" t="str">
+      <x:c r="F34" s="13" t="str"/>
+      <x:c r="G34" s="13" t="str"/>
+      <x:c r="H34" s="13" t="str"/>
+      <x:c r="I34" s="13" t="str"/>
+      <x:c r="J34" s="13" t="str"/>
+      <x:c r="K34" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3826,17 +4470,21 @@
       <x:c r="B35" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C35" s="15" t="str">
+      <x:c r="C35" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D35" s="15" t="str">
+      <x:c r="D35" s="13" t="str">
         <x:v>Download throughput is calculated correctly</x:v>
       </x:c>
-      <x:c r="E35" s="15" t="str">
+      <x:c r="E35" s="13" t="str">
         <x:v>Measurement report</x:v>
       </x:c>
-      <x:c r="F35" s="15" t="str"/>
-      <x:c r="G35" t="str">
+      <x:c r="F35" s="13" t="str"/>
+      <x:c r="G35" s="13" t="str"/>
+      <x:c r="H35" s="13" t="str"/>
+      <x:c r="I35" s="13" t="str"/>
+      <x:c r="J35" s="13" t="str"/>
+      <x:c r="K35" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3847,17 +4495,21 @@
       <x:c r="B36" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C36" s="15" t="str">
+      <x:c r="C36" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D36" s="15" t="str">
+      <x:c r="D36" s="13" t="str">
         <x:v>Upload throughput is calculated correctly</x:v>
       </x:c>
-      <x:c r="E36" s="15" t="str">
+      <x:c r="E36" s="13" t="str">
         <x:v>Measurement report</x:v>
       </x:c>
-      <x:c r="F36" s="15" t="str"/>
-      <x:c r="G36" t="str">
+      <x:c r="F36" s="13" t="str"/>
+      <x:c r="G36" s="13" t="str"/>
+      <x:c r="H36" s="13" t="str"/>
+      <x:c r="I36" s="13" t="str"/>
+      <x:c r="J36" s="13" t="str"/>
+      <x:c r="K36" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3868,17 +4520,21 @@
       <x:c r="B37" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C37" s="15" t="str">
+      <x:c r="C37" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D37" s="15" t="str">
+      <x:c r="D37" s="13" t="str">
         <x:v>Latency is calculated correctly</x:v>
       </x:c>
-      <x:c r="E37" s="15" t="str">
+      <x:c r="E37" s="13" t="str">
         <x:v>Measurement report</x:v>
       </x:c>
-      <x:c r="F37" s="15" t="str"/>
-      <x:c r="G37" t="str">
+      <x:c r="F37" s="13" t="str"/>
+      <x:c r="G37" s="13" t="str"/>
+      <x:c r="H37" s="13" t="str"/>
+      <x:c r="I37" s="13" t="str"/>
+      <x:c r="J37" s="13" t="str"/>
+      <x:c r="K37" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3889,17 +4545,21 @@
       <x:c r="B38" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C38" s="15" t="str">
+      <x:c r="C38" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D38" s="15" t="str">
+      <x:c r="D38" s="13" t="str">
         <x:v>Packet Loss is calculated correctly</x:v>
       </x:c>
-      <x:c r="E38" s="15" t="str">
+      <x:c r="E38" s="13" t="str">
         <x:v>Measurement report</x:v>
       </x:c>
-      <x:c r="F38" s="15" t="str"/>
-      <x:c r="G38" t="str">
+      <x:c r="F38" s="13" t="str"/>
+      <x:c r="G38" s="13" t="str"/>
+      <x:c r="H38" s="13" t="str"/>
+      <x:c r="I38" s="13" t="str"/>
+      <x:c r="J38" s="13" t="str"/>
+      <x:c r="K38" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3910,17 +4570,21 @@
       <x:c r="B39" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C39" s="15" t="str">
+      <x:c r="C39" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D39" s="15" t="str">
+      <x:c r="D39" s="13" t="str">
         <x:v>Result is reviewed before submission</x:v>
       </x:c>
-      <x:c r="E39" s="15" t="str">
+      <x:c r="E39" s="13" t="str">
         <x:v>Review email / sign-off / checker remarks</x:v>
       </x:c>
-      <x:c r="F39" s="15" t="str"/>
-      <x:c r="G39" t="str">
+      <x:c r="F39" s="13" t="str"/>
+      <x:c r="G39" s="13" t="str"/>
+      <x:c r="H39" s="13" t="str"/>
+      <x:c r="I39" s="13" t="str"/>
+      <x:c r="J39" s="13" t="str"/>
+      <x:c r="K39" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3931,17 +4595,21 @@
       <x:c r="B40" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C40" s="15" t="str">
+      <x:c r="C40" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D40" s="15" t="str">
+      <x:c r="D40" s="13" t="str">
         <x:v>Raw result matches submitted tracker/report</x:v>
       </x:c>
-      <x:c r="E40" s="15" t="str">
+      <x:c r="E40" s="13" t="str">
         <x:v>Sampling check between raw result, report and tracker</x:v>
       </x:c>
-      <x:c r="F40" s="15" t="str"/>
-      <x:c r="G40" t="str">
+      <x:c r="F40" s="13" t="str"/>
+      <x:c r="G40" s="13" t="str"/>
+      <x:c r="H40" s="13" t="str"/>
+      <x:c r="I40" s="13" t="str"/>
+      <x:c r="J40" s="13" t="str"/>
+      <x:c r="K40" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3952,17 +4620,21 @@
       <x:c r="B41" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C41" s="15" t="str">
+      <x:c r="C41" s="13" t="str">
         <x:v>C. Post-Measurement / Analysis</x:v>
       </x:c>
-      <x:c r="D41" s="15" t="str">
+      <x:c r="D41" s="13" t="str">
         <x:v>Assumption, exclusion or limitation is documented</x:v>
       </x:c>
-      <x:c r="E41" s="15" t="str">
+      <x:c r="E41" s="13" t="str">
         <x:v>Analysis note / justification</x:v>
       </x:c>
-      <x:c r="F41" s="15" t="str"/>
-      <x:c r="G41" t="str">
+      <x:c r="F41" s="13" t="str"/>
+      <x:c r="G41" s="13" t="str"/>
+      <x:c r="H41" s="13" t="str"/>
+      <x:c r="I41" s="13" t="str"/>
+      <x:c r="J41" s="13" t="str"/>
+      <x:c r="K41" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3973,17 +4645,21 @@
       <x:c r="B42" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C42" s="15" t="str">
+      <x:c r="C42" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D42" s="15" t="str">
+      <x:c r="D42" s="13" t="str">
         <x:v>Measurement result is entered into Wired BAS Tracker</x:v>
       </x:c>
-      <x:c r="E42" s="15" t="str">
+      <x:c r="E42" s="13" t="str">
         <x:v>Wired BAS Tracker screenshot / system record</x:v>
       </x:c>
-      <x:c r="F42" s="15" t="str"/>
-      <x:c r="G42" t="str">
+      <x:c r="F42" s="13" t="str"/>
+      <x:c r="G42" s="13" t="str"/>
+      <x:c r="H42" s="13" t="str"/>
+      <x:c r="I42" s="13" t="str"/>
+      <x:c r="J42" s="13" t="str"/>
+      <x:c r="K42" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -3994,17 +4670,21 @@
       <x:c r="B43" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C43" s="15" t="str">
+      <x:c r="C43" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D43" s="15" t="str">
+      <x:c r="D43" s="13" t="str">
         <x:v>Mandatory tracker fields are completed</x:v>
       </x:c>
-      <x:c r="E43" s="15" t="str">
+      <x:c r="E43" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F43" s="15" t="str"/>
-      <x:c r="G43" t="str">
+      <x:c r="F43" s="13" t="str"/>
+      <x:c r="G43" s="13" t="str"/>
+      <x:c r="H43" s="13" t="str"/>
+      <x:c r="I43" s="13" t="str"/>
+      <x:c r="J43" s="13" t="str"/>
+      <x:c r="K43" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -4015,17 +4695,21 @@
       <x:c r="B44" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C44" s="15" t="str">
+      <x:c r="C44" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D44" s="15" t="str">
+      <x:c r="D44" s="13" t="str">
         <x:v>Operator is selected correctly</x:v>
       </x:c>
-      <x:c r="E44" s="15" t="str">
+      <x:c r="E44" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F44" s="15" t="str"/>
-      <x:c r="G44" t="str">
+      <x:c r="F44" s="13" t="str"/>
+      <x:c r="G44" s="13" t="str"/>
+      <x:c r="H44" s="13" t="str"/>
+      <x:c r="I44" s="13" t="str"/>
+      <x:c r="J44" s="13" t="str"/>
+      <x:c r="K44" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -4036,17 +4720,21 @@
       <x:c r="B45" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C45" s="15" t="str">
+      <x:c r="C45" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D45" s="15" t="str">
+      <x:c r="D45" s="13" t="str">
         <x:v>Download/ Upload/ Latency/ Packet Loss fields are completed</x:v>
       </x:c>
-      <x:c r="E45" s="15" t="str">
+      <x:c r="E45" s="13" t="str">
         <x:v>Tracker review</x:v>
       </x:c>
-      <x:c r="F45" s="15" t="str"/>
-      <x:c r="G45" t="str">
+      <x:c r="F45" s="13" t="str"/>
+      <x:c r="G45" s="13" t="str"/>
+      <x:c r="H45" s="13" t="str"/>
+      <x:c r="I45" s="13" t="str"/>
+      <x:c r="J45" s="13" t="str"/>
+      <x:c r="K45" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -4057,17 +4745,21 @@
       <x:c r="B46" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C46" s="15" t="str">
+      <x:c r="C46" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D46" s="15" t="str">
+      <x:c r="D46" s="13" t="str">
         <x:v>Notice / CD status is supported by evidence</x:v>
       </x:c>
-      <x:c r="E46" s="15" t="str">
+      <x:c r="E46" s="13" t="str">
         <x:v>Tracker + report + email</x:v>
       </x:c>
-      <x:c r="F46" s="15" t="str"/>
-      <x:c r="G46" t="str">
+      <x:c r="F46" s="13" t="str"/>
+      <x:c r="G46" s="13" t="str"/>
+      <x:c r="H46" s="13" t="str"/>
+      <x:c r="I46" s="13" t="str"/>
+      <x:c r="J46" s="13" t="str"/>
+      <x:c r="K46" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -4078,17 +4770,21 @@
       <x:c r="B47" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C47" s="15" t="str">
+      <x:c r="C47" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D47" s="15" t="str">
+      <x:c r="D47" s="13" t="str">
         <x:v>FIR / Notice / CD reference is filled where applicable</x:v>
       </x:c>
-      <x:c r="E47" s="15" t="str">
+      <x:c r="E47" s="13" t="str">
         <x:v>Notice / FIR / CD record</x:v>
       </x:c>
-      <x:c r="F47" s="15" t="str"/>
-      <x:c r="G47" t="str">
+      <x:c r="F47" s="13" t="str"/>
+      <x:c r="G47" s="13" t="str"/>
+      <x:c r="H47" s="13" t="str"/>
+      <x:c r="I47" s="13" t="str"/>
+      <x:c r="J47" s="13" t="str"/>
+      <x:c r="K47" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -4099,17 +4795,21 @@
       <x:c r="B48" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C48" s="15" t="str">
+      <x:c r="C48" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D48" s="15" t="str">
+      <x:c r="D48" s="13" t="str">
         <x:v>MNO is notified where required</x:v>
       </x:c>
-      <x:c r="E48" s="15" t="str">
+      <x:c r="E48" s="13" t="str">
         <x:v>Email / letter</x:v>
       </x:c>
-      <x:c r="F48" s="15" t="str"/>
-      <x:c r="G48" t="str">
+      <x:c r="F48" s="13" t="str"/>
+      <x:c r="G48" s="13" t="str"/>
+      <x:c r="H48" s="13" t="str"/>
+      <x:c r="I48" s="13" t="str"/>
+      <x:c r="J48" s="13" t="str"/>
+      <x:c r="K48" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -4120,17 +4820,21 @@
       <x:c r="B49" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C49" s="15" t="str">
+      <x:c r="C49" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D49" s="15" t="str">
+      <x:c r="D49" s="13" t="str">
         <x:v>Reminder is issued if MNO does not respond</x:v>
       </x:c>
-      <x:c r="E49" s="15" t="str">
+      <x:c r="E49" s="13" t="str">
         <x:v>Follow-up email</x:v>
       </x:c>
-      <x:c r="F49" s="15" t="str"/>
-      <x:c r="G49" t="str">
+      <x:c r="F49" s="13" t="str"/>
+      <x:c r="G49" s="13" t="str"/>
+      <x:c r="H49" s="13" t="str"/>
+      <x:c r="I49" s="13" t="str"/>
+      <x:c r="J49" s="13" t="str"/>
+      <x:c r="K49" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -4141,26 +4845,30 @@
       <x:c r="B50" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C50" s="15" t="str">
+      <x:c r="C50" s="13" t="str">
         <x:v>D. Tracker / Reporting / Follow-Up</x:v>
       </x:c>
-      <x:c r="D50" s="15" t="str">
+      <x:c r="D50" s="13" t="str">
         <x:v>Case is closed only with complete evidence</x:v>
       </x:c>
-      <x:c r="E50" s="15" t="str">
+      <x:c r="E50" s="13" t="str">
         <x:v>Closure note / final response / final tracker status</x:v>
       </x:c>
-      <x:c r="F50" s="15" t="str"/>
-      <x:c r="G50" t="str">
+      <x:c r="F50" s="13" t="str"/>
+      <x:c r="G50" s="13" t="str"/>
+      <x:c r="H50" s="13" t="str"/>
+      <x:c r="I50" s="13" t="str"/>
+      <x:c r="J50" s="13" t="str"/>
+      <x:c r="K50" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A1:K1"/>
   </x:mergeCells>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="G11:G50">
+    <x:dataValidation type="list" sqref="K11:K50">
       <x:formula1>"Yes,No"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
